--- a/price.xlsx
+++ b/price.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t>浅海</t>
   </si>
@@ -112,6 +112,51 @@
     <t>分布标准差σ</t>
   </si>
   <si>
+    <t>巨型饵鱼</t>
+  </si>
+  <si>
+    <t>巨型波爬</t>
+  </si>
+  <si>
+    <t>鱿鱼饵</t>
+  </si>
+  <si>
+    <t>饵鱼</t>
+  </si>
+  <si>
+    <t>波趴</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 螺肉</t>
+  </si>
+  <si>
+    <t>鱼块</t>
+  </si>
+  <si>
+    <t>铅笔</t>
+  </si>
+  <si>
+    <t>贝肉</t>
+  </si>
+  <si>
+    <t>鱼条</t>
+  </si>
+  <si>
+    <t>亮片</t>
+  </si>
+  <si>
+    <t>虾肉</t>
+  </si>
+  <si>
+    <t>人造饵</t>
+  </si>
+  <si>
+    <t>瓜子亮片</t>
+  </si>
+  <si>
+    <t>南极磷虾</t>
+  </si>
+  <si>
     <t>翻车鱼</t>
   </si>
   <si>
@@ -160,7 +205,7 @@
     <t>月鱼</t>
   </si>
   <si>
-    <t>大海鲢</t>
+    <t>海湾鲟</t>
   </si>
   <si>
     <t>高体鰤</t>
@@ -485,12 +530,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -826,7 +895,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -850,16 +919,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
@@ -868,25 +937,13 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
@@ -949,8 +1006,20 @@
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -958,7 +1027,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1270,10 +1346,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA68"/>
+  <dimension ref="A1:AP68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:42">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1355,8 +1431,53 @@
       <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:42">
       <c r="A2" s="1">
         <v>0.03</v>
       </c>
@@ -1417,8 +1538,8 @@
       <c r="T2" s="1">
         <v>6</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>27</v>
+      <c r="U2" s="4" t="s">
+        <v>42</v>
       </c>
       <c r="V2" s="1">
         <v>150</v>
@@ -1438,8 +1559,26 @@
       <c r="AA2" s="1">
         <v>290.25</v>
       </c>
+      <c r="AB2">
+        <v>2</v>
+      </c>
+      <c r="AC2">
+        <v>5</v>
+      </c>
+      <c r="AD2">
+        <v>1</v>
+      </c>
+      <c r="AE2">
+        <v>2</v>
+      </c>
+      <c r="AF2">
+        <v>2</v>
+      </c>
+      <c r="AG2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:42">
       <c r="A3" s="1">
         <v>0.02</v>
       </c>
@@ -1500,8 +1639,8 @@
       <c r="T3" s="1">
         <v>22</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>28</v>
+      <c r="U3" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="V3" s="1">
         <v>30</v>
@@ -1521,8 +1660,26 @@
       <c r="AA3" s="1">
         <v>87.75</v>
       </c>
+      <c r="AB3">
+        <v>2</v>
+      </c>
+      <c r="AC3">
+        <v>5</v>
+      </c>
+      <c r="AD3">
+        <v>1</v>
+      </c>
+      <c r="AE3">
+        <v>2</v>
+      </c>
+      <c r="AF3">
+        <v>2</v>
+      </c>
+      <c r="AG3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:42">
       <c r="A4" s="1">
         <v>0.09</v>
       </c>
@@ -1583,8 +1740,8 @@
       <c r="T4" s="1">
         <v>17</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>29</v>
+      <c r="U4" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="V4" s="1">
         <v>37.5</v>
@@ -1604,8 +1761,26 @@
       <c r="AA4" s="1">
         <v>62.4375</v>
       </c>
+      <c r="AB4">
+        <v>2</v>
+      </c>
+      <c r="AC4">
+        <v>1</v>
+      </c>
+      <c r="AD4">
+        <v>5</v>
+      </c>
+      <c r="AE4">
+        <v>2</v>
+      </c>
+      <c r="AF4">
+        <v>2</v>
+      </c>
+      <c r="AG4">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:42">
       <c r="A5" s="1">
         <v>0.1</v>
       </c>
@@ -1666,8 +1841,8 @@
       <c r="T5" s="1">
         <v>15</v>
       </c>
-      <c r="U5" s="1" t="s">
-        <v>30</v>
+      <c r="U5" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="V5" s="1">
         <v>6</v>
@@ -1687,8 +1862,26 @@
       <c r="AA5" s="1">
         <v>31.59</v>
       </c>
+      <c r="AB5">
+        <v>2</v>
+      </c>
+      <c r="AC5">
+        <v>5</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>2</v>
+      </c>
+      <c r="AF5">
+        <v>2</v>
+      </c>
+      <c r="AG5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:42">
       <c r="A6" s="1">
         <v>0.08</v>
       </c>
@@ -1749,8 +1942,8 @@
       <c r="T6" s="1">
         <v>17</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>31</v>
+      <c r="U6" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="V6" s="1">
         <v>7.5</v>
@@ -1770,8 +1963,26 @@
       <c r="AA6" s="1">
         <v>39.4875</v>
       </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <v>2</v>
+      </c>
+      <c r="AF6">
+        <v>2</v>
+      </c>
+      <c r="AG6">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:42">
       <c r="A7" s="1">
         <v>0.08</v>
       </c>
@@ -1832,8 +2043,8 @@
       <c r="T7" s="1">
         <v>4</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>32</v>
+      <c r="U7" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="V7" s="1">
         <v>15</v>
@@ -1853,8 +2064,26 @@
       <c r="AA7" s="1">
         <v>38.475</v>
       </c>
+      <c r="AB7">
+        <v>2</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>5</v>
+      </c>
+      <c r="AE7">
+        <v>2</v>
+      </c>
+      <c r="AF7">
+        <v>2</v>
+      </c>
+      <c r="AG7">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:42">
       <c r="A8" s="1">
         <v>0.15</v>
       </c>
@@ -1915,8 +2144,8 @@
       <c r="T8" s="1">
         <v>22</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>33</v>
+      <c r="U8" s="4" t="s">
+        <v>48</v>
       </c>
       <c r="V8" s="1">
         <v>15</v>
@@ -1936,8 +2165,26 @@
       <c r="AA8" s="1">
         <v>34.425</v>
       </c>
+      <c r="AB8">
+        <v>2</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>5</v>
+      </c>
+      <c r="AE8">
+        <v>2</v>
+      </c>
+      <c r="AF8">
+        <v>2</v>
+      </c>
+      <c r="AG8">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:42">
       <c r="A9" s="1">
         <v>0.03</v>
       </c>
@@ -1998,8 +2245,8 @@
       <c r="T9" s="1">
         <v>7</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>34</v>
+      <c r="U9" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="V9" s="1">
         <v>18</v>
@@ -2019,8 +2266,26 @@
       <c r="AA9" s="1">
         <v>31.32</v>
       </c>
+      <c r="AB9">
+        <v>2</v>
+      </c>
+      <c r="AC9">
+        <v>5</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>2</v>
+      </c>
+      <c r="AF9">
+        <v>2</v>
+      </c>
+      <c r="AG9">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:42">
       <c r="A10" s="1">
         <v>0.04</v>
       </c>
@@ -2081,8 +2346,8 @@
       <c r="T10" s="1">
         <v>12</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>35</v>
+      <c r="U10" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="V10" s="1">
         <v>12</v>
@@ -2102,8 +2367,26 @@
       <c r="AA10" s="1">
         <v>25.38</v>
       </c>
+      <c r="AB10">
+        <v>2</v>
+      </c>
+      <c r="AC10">
+        <v>5</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>2</v>
+      </c>
+      <c r="AF10">
+        <v>2</v>
+      </c>
+      <c r="AG10">
+        <v>2</v>
+      </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:42">
       <c r="A11" s="1">
         <v>0.68</v>
       </c>
@@ -2140,7 +2423,7 @@
       <c r="L11" s="1">
         <v>0.05</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="5">
         <v>0.2</v>
       </c>
       <c r="N11" s="1">
@@ -2164,8 +2447,8 @@
       <c r="T11" s="1">
         <v>10</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>36</v>
+      <c r="U11" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="V11" s="1">
         <v>12</v>
@@ -2185,8 +2468,26 @@
       <c r="AA11" s="1">
         <v>18.63</v>
       </c>
+      <c r="AB11">
+        <v>2</v>
+      </c>
+      <c r="AC11">
+        <v>5</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>2</v>
+      </c>
+      <c r="AF11">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>2</v>
+      </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:42">
       <c r="A12" s="1">
         <v>0.03</v>
       </c>
@@ -2223,7 +2524,7 @@
       <c r="L12" s="1">
         <v>0.05</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="5">
         <v>0.2</v>
       </c>
       <c r="N12" s="1">
@@ -2247,8 +2548,8 @@
       <c r="T12" s="1">
         <v>17</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>37</v>
+      <c r="U12" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="V12" s="1">
         <v>6</v>
@@ -2268,8 +2569,26 @@
       <c r="AA12" s="1">
         <v>12.69</v>
       </c>
+      <c r="AB12">
+        <v>2</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>5</v>
+      </c>
+      <c r="AE12">
+        <v>2</v>
+      </c>
+      <c r="AF12">
+        <v>2</v>
+      </c>
+      <c r="AG12">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:42">
       <c r="A13" s="1">
         <v>0.07</v>
       </c>
@@ -2306,7 +2625,7 @@
       <c r="L13" s="1">
         <v>0.05</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="5">
         <v>0.2</v>
       </c>
       <c r="N13" s="1">
@@ -2330,8 +2649,8 @@
       <c r="T13" s="1">
         <v>6</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>38</v>
+      <c r="U13" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="V13" s="1">
         <v>4.5</v>
@@ -2351,8 +2670,26 @@
       <c r="AA13" s="1">
         <v>12.8925</v>
       </c>
+      <c r="AB13">
+        <v>2</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>5</v>
+      </c>
+      <c r="AE13">
+        <v>2</v>
+      </c>
+      <c r="AF13">
+        <v>2</v>
+      </c>
+      <c r="AG13">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:42">
       <c r="A14" s="1">
         <v>0.1</v>
       </c>
@@ -2413,8 +2750,8 @@
       <c r="T14" s="1">
         <v>4</v>
       </c>
-      <c r="U14" s="1" t="s">
-        <v>39</v>
+      <c r="U14" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="V14" s="1">
         <v>2.25</v>
@@ -2434,8 +2771,35 @@
       <c r="AA14" s="1">
         <v>10.4962</v>
       </c>
+      <c r="AB14">
+        <v>2</v>
+      </c>
+      <c r="AC14">
+        <v>2</v>
+      </c>
+      <c r="AD14">
+        <v>2</v>
+      </c>
+      <c r="AE14">
+        <v>2</v>
+      </c>
+      <c r="AF14">
+        <v>5</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>2</v>
+      </c>
+      <c r="AI14">
+        <v>2</v>
+      </c>
+      <c r="AJ14">
+        <v>2</v>
+      </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:42">
       <c r="A15" s="1">
         <v>0.01</v>
       </c>
@@ -2496,8 +2860,8 @@
       <c r="T15" s="1">
         <v>7</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>40</v>
+      <c r="U15" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="V15" s="1">
         <v>3</v>
@@ -2517,8 +2881,35 @@
       <c r="AA15" s="1">
         <v>9.045</v>
       </c>
+      <c r="AB15">
+        <v>2</v>
+      </c>
+      <c r="AC15">
+        <v>2</v>
+      </c>
+      <c r="AD15">
+        <v>2</v>
+      </c>
+      <c r="AE15">
+        <v>2</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>5</v>
+      </c>
+      <c r="AH15">
+        <v>2</v>
+      </c>
+      <c r="AI15">
+        <v>2</v>
+      </c>
+      <c r="AJ15">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:42">
       <c r="A16" s="1">
         <v>0.05</v>
       </c>
@@ -2579,8 +2970,8 @@
       <c r="T16" s="1">
         <v>12</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>41</v>
+      <c r="U16" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="V16" s="1">
         <v>5.25</v>
@@ -2600,8 +2991,35 @@
       <c r="AA16" s="1">
         <v>8.7413</v>
       </c>
+      <c r="AB16">
+        <v>2</v>
+      </c>
+      <c r="AC16">
+        <v>2</v>
+      </c>
+      <c r="AD16">
+        <v>2</v>
+      </c>
+      <c r="AE16">
+        <v>2</v>
+      </c>
+      <c r="AF16">
+        <v>5</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>2</v>
+      </c>
+      <c r="AI16">
+        <v>2</v>
+      </c>
+      <c r="AJ16">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:42">
       <c r="A17" s="1">
         <v>0.05</v>
       </c>
@@ -2662,8 +3080,8 @@
       <c r="T17" s="1">
         <v>17</v>
       </c>
-      <c r="U17" s="1" t="s">
-        <v>42</v>
+      <c r="U17" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="V17" s="1">
         <v>3</v>
@@ -2683,8 +3101,35 @@
       <c r="AA17" s="1">
         <v>26.595</v>
       </c>
+      <c r="AB17">
+        <v>2</v>
+      </c>
+      <c r="AC17">
+        <v>2</v>
+      </c>
+      <c r="AD17">
+        <v>2</v>
+      </c>
+      <c r="AE17">
+        <v>2</v>
+      </c>
+      <c r="AF17">
+        <v>5</v>
+      </c>
+      <c r="AG17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>2</v>
+      </c>
+      <c r="AI17">
+        <v>2</v>
+      </c>
+      <c r="AJ17">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:27">
+    <row r="18" spans="1:42">
       <c r="A18" s="1">
         <v>0.08</v>
       </c>
@@ -2745,8 +3190,8 @@
       <c r="T18" s="1">
         <v>10</v>
       </c>
-      <c r="U18" s="1" t="s">
-        <v>43</v>
+      <c r="U18" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="V18" s="1">
         <v>2.25</v>
@@ -2766,8 +3211,35 @@
       <c r="AA18" s="1">
         <v>19.2713</v>
       </c>
+      <c r="AB18">
+        <v>2</v>
+      </c>
+      <c r="AC18">
+        <v>2</v>
+      </c>
+      <c r="AD18">
+        <v>2</v>
+      </c>
+      <c r="AE18">
+        <v>2</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <v>5</v>
+      </c>
+      <c r="AH18">
+        <v>2</v>
+      </c>
+      <c r="AI18">
+        <v>2</v>
+      </c>
+      <c r="AJ18">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:27">
+    <row r="19" spans="1:42">
       <c r="A19" s="1">
         <v>0.06</v>
       </c>
@@ -2828,8 +3300,8 @@
       <c r="T19" s="1">
         <v>7</v>
       </c>
-      <c r="U19" s="1" t="s">
-        <v>44</v>
+      <c r="U19" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="V19" s="1">
         <v>1.2</v>
@@ -2849,8 +3321,35 @@
       <c r="AA19" s="1">
         <v>9.558</v>
       </c>
+      <c r="AB19">
+        <v>2</v>
+      </c>
+      <c r="AC19">
+        <v>2</v>
+      </c>
+      <c r="AD19">
+        <v>2</v>
+      </c>
+      <c r="AE19">
+        <v>2</v>
+      </c>
+      <c r="AF19">
+        <v>5</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>2</v>
+      </c>
+      <c r="AI19">
+        <v>2</v>
+      </c>
+      <c r="AJ19">
+        <v>2</v>
+      </c>
     </row>
-    <row r="20" spans="1:27">
+    <row r="20" spans="1:42">
       <c r="A20" s="1">
         <v>0.13</v>
       </c>
@@ -2881,7 +3380,7 @@
       <c r="J20" s="1">
         <v>0.75</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="5">
         <v>0.2</v>
       </c>
       <c r="L20" s="1">
@@ -2912,7 +3411,7 @@
         <v>10</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="V20" s="1">
         <v>0.09</v>
@@ -2932,8 +3431,26 @@
       <c r="AA20" s="1">
         <v>0.1904</v>
       </c>
+      <c r="AK20">
+        <v>2</v>
+      </c>
+      <c r="AL20">
+        <v>2</v>
+      </c>
+      <c r="AM20">
+        <v>2</v>
+      </c>
+      <c r="AN20">
+        <v>2</v>
+      </c>
+      <c r="AO20">
+        <v>5</v>
+      </c>
+      <c r="AP20">
+        <v>1</v>
+      </c>
     </row>
-    <row r="21" spans="1:27">
+    <row r="21" spans="1:42">
       <c r="A21" s="1">
         <v>0.17</v>
       </c>
@@ -2964,7 +3481,7 @@
       <c r="J21" s="1">
         <v>0.2</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="5">
         <v>0.6</v>
       </c>
       <c r="L21" s="1">
@@ -2994,8 +3511,8 @@
       <c r="T21" s="1">
         <v>27</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>46</v>
+      <c r="U21" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="V21" s="1">
         <v>0.3</v>
@@ -3015,8 +3532,35 @@
       <c r="AA21" s="1">
         <v>0.6345</v>
       </c>
+      <c r="AH21">
+        <v>2</v>
+      </c>
+      <c r="AI21">
+        <v>2</v>
+      </c>
+      <c r="AJ21">
+        <v>2</v>
+      </c>
+      <c r="AK21">
+        <v>2</v>
+      </c>
+      <c r="AL21">
+        <v>1</v>
+      </c>
+      <c r="AM21">
+        <v>5</v>
+      </c>
+      <c r="AN21">
+        <v>2</v>
+      </c>
+      <c r="AO21">
+        <v>2</v>
+      </c>
+      <c r="AP21">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:27">
+    <row r="22" spans="1:42">
       <c r="A22" s="1">
         <v>0.04</v>
       </c>
@@ -3077,8 +3621,8 @@
       <c r="T22" s="1">
         <v>14</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>47</v>
+      <c r="U22" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="V22" s="1">
         <v>0.45</v>
@@ -3098,8 +3642,35 @@
       <c r="AA22" s="1">
         <v>3.1792</v>
       </c>
+      <c r="AE22">
+        <v>2</v>
+      </c>
+      <c r="AF22">
+        <v>2</v>
+      </c>
+      <c r="AG22">
+        <v>2</v>
+      </c>
+      <c r="AH22">
+        <v>2</v>
+      </c>
+      <c r="AI22">
+        <v>1</v>
+      </c>
+      <c r="AJ22">
+        <v>5</v>
+      </c>
+      <c r="AK22">
+        <v>2</v>
+      </c>
+      <c r="AL22">
+        <v>2</v>
+      </c>
+      <c r="AM22">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:27">
+    <row r="23" spans="1:42">
       <c r="A23" s="1">
         <v>0.08</v>
       </c>
@@ -3160,8 +3731,8 @@
       <c r="T23" s="1">
         <v>7</v>
       </c>
-      <c r="U23" s="1" t="s">
-        <v>48</v>
+      <c r="U23" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="V23" s="1">
         <v>0.75</v>
@@ -3181,8 +3752,35 @@
       <c r="AA23" s="1">
         <v>5.9738</v>
       </c>
+      <c r="AE23">
+        <v>2</v>
+      </c>
+      <c r="AF23">
+        <v>2</v>
+      </c>
+      <c r="AG23">
+        <v>2</v>
+      </c>
+      <c r="AH23">
+        <v>2</v>
+      </c>
+      <c r="AI23">
+        <v>5</v>
+      </c>
+      <c r="AJ23">
+        <v>1</v>
+      </c>
+      <c r="AK23">
+        <v>2</v>
+      </c>
+      <c r="AL23">
+        <v>2</v>
+      </c>
+      <c r="AM23">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:27">
+    <row r="24" spans="1:42">
       <c r="A24" s="1">
         <v>0.13</v>
       </c>
@@ -3243,8 +3841,8 @@
       <c r="T24" s="1">
         <v>4</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>49</v>
+      <c r="U24" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="V24" s="1">
         <v>0.45</v>
@@ -3264,8 +3862,35 @@
       <c r="AA24" s="1">
         <v>2.6392</v>
       </c>
+      <c r="AE24">
+        <v>2</v>
+      </c>
+      <c r="AF24">
+        <v>2</v>
+      </c>
+      <c r="AG24">
+        <v>2</v>
+      </c>
+      <c r="AH24">
+        <v>2</v>
+      </c>
+      <c r="AI24">
+        <v>1</v>
+      </c>
+      <c r="AJ24">
+        <v>5</v>
+      </c>
+      <c r="AK24">
+        <v>2</v>
+      </c>
+      <c r="AL24">
+        <v>2</v>
+      </c>
+      <c r="AM24">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:27">
+    <row r="25" spans="1:42">
       <c r="A25" s="1">
         <v>0.88</v>
       </c>
@@ -3326,8 +3951,8 @@
       <c r="T25" s="1">
         <v>6</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>50</v>
+      <c r="U25" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="V25" s="1">
         <v>1.8</v>
@@ -3347,8 +3972,35 @@
       <c r="AA25" s="1">
         <v>18.657</v>
       </c>
+      <c r="AB25">
+        <v>2</v>
+      </c>
+      <c r="AC25">
+        <v>2</v>
+      </c>
+      <c r="AD25">
+        <v>2</v>
+      </c>
+      <c r="AE25">
+        <v>2</v>
+      </c>
+      <c r="AF25">
+        <v>5</v>
+      </c>
+      <c r="AG25">
+        <v>1</v>
+      </c>
+      <c r="AH25">
+        <v>2</v>
+      </c>
+      <c r="AI25">
+        <v>2</v>
+      </c>
+      <c r="AJ25">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:27">
+    <row r="26" spans="1:42">
       <c r="A26" s="1">
         <v>0.07</v>
       </c>
@@ -3379,7 +4031,7 @@
       <c r="J26" s="1">
         <v>0.2</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="5">
         <v>0.6</v>
       </c>
       <c r="L26" s="1">
@@ -3409,8 +4061,8 @@
       <c r="T26" s="1">
         <v>16</v>
       </c>
-      <c r="U26" s="1" t="s">
-        <v>51</v>
+      <c r="U26" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="V26" s="1">
         <v>0.15</v>
@@ -3430,8 +4082,35 @@
       <c r="AA26" s="1">
         <v>1.3298</v>
       </c>
+      <c r="AH26">
+        <v>2</v>
+      </c>
+      <c r="AI26">
+        <v>2</v>
+      </c>
+      <c r="AJ26">
+        <v>2</v>
+      </c>
+      <c r="AK26">
+        <v>2</v>
+      </c>
+      <c r="AL26">
+        <v>5</v>
+      </c>
+      <c r="AM26">
+        <v>1</v>
+      </c>
+      <c r="AN26">
+        <v>2</v>
+      </c>
+      <c r="AO26">
+        <v>2</v>
+      </c>
+      <c r="AP26">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:27">
+    <row r="27" spans="1:42">
       <c r="A27" s="1">
         <v>0.1</v>
       </c>
@@ -3492,8 +4171,8 @@
       <c r="T27" s="1">
         <v>47</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>52</v>
+      <c r="U27" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="V27" s="1">
         <v>0.375</v>
@@ -3514,7 +4193,7 @@
         <v>2.6494</v>
       </c>
     </row>
-    <row r="28" spans="1:27">
+    <row r="28" spans="1:42">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -3545,7 +4224,7 @@
       <c r="J28" s="1">
         <v>0.2</v>
       </c>
-      <c r="K28" s="3">
+      <c r="K28" s="5">
         <v>0.6</v>
       </c>
       <c r="L28" s="1">
@@ -3575,8 +4254,8 @@
       <c r="T28" s="1">
         <v>7</v>
       </c>
-      <c r="U28" s="1" t="s">
-        <v>53</v>
+      <c r="U28" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="V28" s="1">
         <v>0.225</v>
@@ -3596,8 +4275,35 @@
       <c r="AA28" s="1">
         <v>1.3196</v>
       </c>
+      <c r="AH28">
+        <v>2</v>
+      </c>
+      <c r="AI28">
+        <v>2</v>
+      </c>
+      <c r="AJ28">
+        <v>2</v>
+      </c>
+      <c r="AK28">
+        <v>2</v>
+      </c>
+      <c r="AL28">
+        <v>1</v>
+      </c>
+      <c r="AM28">
+        <v>5</v>
+      </c>
+      <c r="AN28">
+        <v>2</v>
+      </c>
+      <c r="AO28">
+        <v>2</v>
+      </c>
+      <c r="AP28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:27">
+    <row r="29" spans="1:42">
       <c r="A29" s="1">
         <v>0.15</v>
       </c>
@@ -3658,8 +4364,8 @@
       <c r="T29" s="1">
         <v>4</v>
       </c>
-      <c r="U29" s="1" t="s">
-        <v>54</v>
+      <c r="U29" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="V29" s="1">
         <v>1.8</v>
@@ -3679,8 +4385,35 @@
       <c r="AA29" s="1">
         <v>6.507</v>
       </c>
+      <c r="AB29">
+        <v>2</v>
+      </c>
+      <c r="AC29">
+        <v>2</v>
+      </c>
+      <c r="AD29">
+        <v>2</v>
+      </c>
+      <c r="AE29">
+        <v>2</v>
+      </c>
+      <c r="AF29">
+        <v>5</v>
+      </c>
+      <c r="AG29">
+        <v>1</v>
+      </c>
+      <c r="AH29">
+        <v>2</v>
+      </c>
+      <c r="AI29">
+        <v>2</v>
+      </c>
+      <c r="AJ29">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:27">
+    <row r="30" spans="1:42">
       <c r="A30" s="1">
         <v>0.09</v>
       </c>
@@ -3711,7 +4444,7 @@
       <c r="J30" s="1">
         <v>0.75</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="5">
         <v>0.2</v>
       </c>
       <c r="L30" s="1">
@@ -3742,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="V30" s="1">
         <v>0.15</v>
@@ -3762,8 +4495,26 @@
       <c r="AA30" s="1">
         <v>0.3848</v>
       </c>
+      <c r="AK30">
+        <v>2</v>
+      </c>
+      <c r="AL30">
+        <v>2</v>
+      </c>
+      <c r="AM30">
+        <v>2</v>
+      </c>
+      <c r="AN30">
+        <v>2</v>
+      </c>
+      <c r="AO30">
+        <v>1</v>
+      </c>
+      <c r="AP30">
+        <v>5</v>
+      </c>
     </row>
-    <row r="31" spans="1:27">
+    <row r="31" spans="1:42">
       <c r="A31" s="1">
         <v>0.06</v>
       </c>
@@ -3794,7 +4545,7 @@
       <c r="J31" s="1">
         <v>0.2</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="5">
         <v>0.6</v>
       </c>
       <c r="L31" s="1">
@@ -3824,8 +4575,8 @@
       <c r="T31" s="1">
         <v>26</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>56</v>
+      <c r="U31" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="V31" s="1">
         <v>0.12</v>
@@ -3845,8 +4596,35 @@
       <c r="AA31" s="1">
         <v>0.7938</v>
       </c>
+      <c r="AH31">
+        <v>2</v>
+      </c>
+      <c r="AI31">
+        <v>2</v>
+      </c>
+      <c r="AJ31">
+        <v>2</v>
+      </c>
+      <c r="AK31">
+        <v>2</v>
+      </c>
+      <c r="AL31">
+        <v>5</v>
+      </c>
+      <c r="AM31">
+        <v>1</v>
+      </c>
+      <c r="AN31">
+        <v>2</v>
+      </c>
+      <c r="AO31">
+        <v>2</v>
+      </c>
+      <c r="AP31">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:27">
+    <row r="32" spans="1:42">
       <c r="A32" s="1">
         <v>0.07</v>
       </c>
@@ -3907,8 +4685,8 @@
       <c r="T32" s="1">
         <v>27</v>
       </c>
-      <c r="U32" s="1" t="s">
-        <v>57</v>
+      <c r="U32" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="V32" s="1">
         <v>0.3</v>
@@ -3928,8 +4706,35 @@
       <c r="AA32" s="1">
         <v>1.5795</v>
       </c>
+      <c r="AE32">
+        <v>2</v>
+      </c>
+      <c r="AF32">
+        <v>2</v>
+      </c>
+      <c r="AG32">
+        <v>2</v>
+      </c>
+      <c r="AH32">
+        <v>2</v>
+      </c>
+      <c r="AI32">
+        <v>1</v>
+      </c>
+      <c r="AJ32">
+        <v>5</v>
+      </c>
+      <c r="AK32">
+        <v>2</v>
+      </c>
+      <c r="AL32">
+        <v>2</v>
+      </c>
+      <c r="AM32">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:27">
+    <row r="33" spans="1:42">
       <c r="A33" s="1">
         <v>0.77</v>
       </c>
@@ -3960,7 +4765,7 @@
       <c r="J33" s="1">
         <v>0.2</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="5">
         <v>0.6</v>
       </c>
       <c r="L33" s="1">
@@ -3990,8 +4795,8 @@
       <c r="T33" s="1">
         <v>4</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>58</v>
+      <c r="U33" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="V33" s="1">
         <v>0.255</v>
@@ -4011,8 +4816,35 @@
       <c r="AA33" s="1">
         <v>0.9106</v>
       </c>
+      <c r="AH33">
+        <v>2</v>
+      </c>
+      <c r="AI33">
+        <v>2</v>
+      </c>
+      <c r="AJ33">
+        <v>2</v>
+      </c>
+      <c r="AK33">
+        <v>2</v>
+      </c>
+      <c r="AL33">
+        <v>5</v>
+      </c>
+      <c r="AM33">
+        <v>1</v>
+      </c>
+      <c r="AN33">
+        <v>2</v>
+      </c>
+      <c r="AO33">
+        <v>2</v>
+      </c>
+      <c r="AP33">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:27">
+    <row r="34" spans="1:42">
       <c r="A34" s="1">
         <v>0.03</v>
       </c>
@@ -4043,7 +4875,7 @@
       <c r="J34" s="1">
         <v>0.2</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="5">
         <v>0.6</v>
       </c>
       <c r="L34" s="1">
@@ -4073,8 +4905,8 @@
       <c r="T34" s="1">
         <v>17</v>
       </c>
-      <c r="U34" s="1" t="s">
-        <v>59</v>
+      <c r="U34" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="V34" s="1">
         <v>0.15</v>
@@ -4094,8 +4926,35 @@
       <c r="AA34" s="1">
         <v>0.3173</v>
       </c>
+      <c r="AH34">
+        <v>2</v>
+      </c>
+      <c r="AI34">
+        <v>2</v>
+      </c>
+      <c r="AJ34">
+        <v>2</v>
+      </c>
+      <c r="AK34">
+        <v>2</v>
+      </c>
+      <c r="AL34">
+        <v>1</v>
+      </c>
+      <c r="AM34">
+        <v>5</v>
+      </c>
+      <c r="AN34">
+        <v>2</v>
+      </c>
+      <c r="AO34">
+        <v>2</v>
+      </c>
+      <c r="AP34">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:27">
+    <row r="35" spans="1:42">
       <c r="A35" s="1">
         <v>0.15</v>
       </c>
@@ -4156,8 +5015,8 @@
       <c r="T35" s="1">
         <v>6</v>
       </c>
-      <c r="U35" s="1" t="s">
-        <v>60</v>
+      <c r="U35" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="V35" s="1">
         <v>0.6</v>
@@ -4177,8 +5036,35 @@
       <c r="AA35" s="1">
         <v>3.294</v>
       </c>
+      <c r="AE35">
+        <v>2</v>
+      </c>
+      <c r="AF35">
+        <v>2</v>
+      </c>
+      <c r="AG35">
+        <v>2</v>
+      </c>
+      <c r="AH35">
+        <v>2</v>
+      </c>
+      <c r="AI35">
+        <v>5</v>
+      </c>
+      <c r="AJ35">
+        <v>1</v>
+      </c>
+      <c r="AK35">
+        <v>2</v>
+      </c>
+      <c r="AL35">
+        <v>2</v>
+      </c>
+      <c r="AM35">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" spans="1:42">
       <c r="A36" s="1">
         <v>0.07</v>
       </c>
@@ -4239,8 +5125,8 @@
       <c r="T36" s="1">
         <v>77</v>
       </c>
-      <c r="U36" s="1" t="s">
-        <v>61</v>
+      <c r="U36" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="V36" s="1">
         <v>0.6</v>
@@ -4260,8 +5146,35 @@
       <c r="AA36" s="1">
         <v>2.889</v>
       </c>
+      <c r="AE36">
+        <v>2</v>
+      </c>
+      <c r="AF36">
+        <v>2</v>
+      </c>
+      <c r="AG36">
+        <v>2</v>
+      </c>
+      <c r="AH36">
+        <v>2</v>
+      </c>
+      <c r="AI36">
+        <v>1</v>
+      </c>
+      <c r="AJ36">
+        <v>5</v>
+      </c>
+      <c r="AK36">
+        <v>2</v>
+      </c>
+      <c r="AL36">
+        <v>2</v>
+      </c>
+      <c r="AM36">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:27">
+    <row r="37" spans="1:42">
       <c r="A37" s="1">
         <v>0.11</v>
       </c>
@@ -4292,7 +5205,7 @@
       <c r="J37" s="1">
         <v>0.2</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="5">
         <v>0.6</v>
       </c>
       <c r="L37" s="1">
@@ -4322,8 +5235,8 @@
       <c r="T37" s="1">
         <v>17</v>
       </c>
-      <c r="U37" s="1" t="s">
-        <v>62</v>
+      <c r="U37" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="V37" s="1">
         <v>0.12</v>
@@ -4343,8 +5256,35 @@
       <c r="AA37" s="1">
         <v>0.7938</v>
       </c>
+      <c r="AH37">
+        <v>2</v>
+      </c>
+      <c r="AI37">
+        <v>2</v>
+      </c>
+      <c r="AJ37">
+        <v>2</v>
+      </c>
+      <c r="AK37">
+        <v>2</v>
+      </c>
+      <c r="AL37">
+        <v>5</v>
+      </c>
+      <c r="AM37">
+        <v>1</v>
+      </c>
+      <c r="AN37">
+        <v>2</v>
+      </c>
+      <c r="AO37">
+        <v>2</v>
+      </c>
+      <c r="AP37">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:27">
+    <row r="38" spans="1:42">
       <c r="A38" s="1">
         <v>0.07</v>
       </c>
@@ -4375,7 +5315,7 @@
       <c r="J38" s="1">
         <v>0.75</v>
       </c>
-      <c r="K38" s="3">
+      <c r="K38" s="5">
         <v>0.2</v>
       </c>
       <c r="L38" s="1">
@@ -4406,7 +5346,7 @@
         <v>20</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="V38" s="1">
         <v>0.12</v>
@@ -4426,8 +5366,26 @@
       <c r="AA38" s="1">
         <v>0.1863</v>
       </c>
+      <c r="AK38">
+        <v>2</v>
+      </c>
+      <c r="AL38">
+        <v>2</v>
+      </c>
+      <c r="AM38">
+        <v>2</v>
+      </c>
+      <c r="AN38">
+        <v>2</v>
+      </c>
+      <c r="AO38">
+        <v>1</v>
+      </c>
+      <c r="AP38">
+        <v>5</v>
+      </c>
     </row>
-    <row r="39" spans="1:27">
+    <row r="39" spans="1:42">
       <c r="A39" s="1">
         <v>0.05</v>
       </c>
@@ -4458,7 +5416,7 @@
       <c r="J39" s="1">
         <v>0.2</v>
       </c>
-      <c r="K39" s="3">
+      <c r="K39" s="5">
         <v>0.6</v>
       </c>
       <c r="L39" s="1">
@@ -4488,8 +5446,8 @@
       <c r="T39" s="1">
         <v>140</v>
       </c>
-      <c r="U39" s="1" t="s">
-        <v>64</v>
+      <c r="U39" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="V39" s="1">
         <v>0.15</v>
@@ -4509,8 +5467,35 @@
       <c r="AA39" s="1">
         <v>0.6547</v>
       </c>
+      <c r="AH39">
+        <v>2</v>
+      </c>
+      <c r="AI39">
+        <v>2</v>
+      </c>
+      <c r="AJ39">
+        <v>2</v>
+      </c>
+      <c r="AK39">
+        <v>2</v>
+      </c>
+      <c r="AL39">
+        <v>1</v>
+      </c>
+      <c r="AM39">
+        <v>5</v>
+      </c>
+      <c r="AN39">
+        <v>2</v>
+      </c>
+      <c r="AO39">
+        <v>2</v>
+      </c>
+      <c r="AP39">
+        <v>2</v>
+      </c>
     </row>
-    <row r="40" spans="1:27">
+    <row r="40" spans="1:42">
       <c r="A40" s="1">
         <v>0.18</v>
       </c>
@@ -4571,8 +5556,8 @@
       <c r="T40" s="1">
         <v>10</v>
       </c>
-      <c r="U40" s="1" t="s">
-        <v>65</v>
+      <c r="U40" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="V40" s="1">
         <v>0.9</v>
@@ -4592,8 +5577,35 @@
       <c r="AA40" s="1">
         <v>2.5785</v>
       </c>
+      <c r="AE40">
+        <v>2</v>
+      </c>
+      <c r="AF40">
+        <v>2</v>
+      </c>
+      <c r="AG40">
+        <v>2</v>
+      </c>
+      <c r="AH40">
+        <v>2</v>
+      </c>
+      <c r="AI40">
+        <v>1</v>
+      </c>
+      <c r="AJ40">
+        <v>5</v>
+      </c>
+      <c r="AK40">
+        <v>2</v>
+      </c>
+      <c r="AL40">
+        <v>2</v>
+      </c>
+      <c r="AM40">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:27">
+    <row r="41" spans="1:42">
       <c r="A41" s="1">
         <v>0.03</v>
       </c>
@@ -4624,7 +5636,7 @@
       <c r="J41" s="1">
         <v>0.2</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="5">
         <v>0.6</v>
       </c>
       <c r="L41" s="1">
@@ -4654,8 +5666,8 @@
       <c r="T41" s="1">
         <v>47</v>
       </c>
-      <c r="U41" s="1" t="s">
-        <v>66</v>
+      <c r="U41" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="V41" s="1">
         <v>0.09</v>
@@ -4675,8 +5687,35 @@
       <c r="AA41" s="1">
         <v>0.5278</v>
       </c>
+      <c r="AH41">
+        <v>2</v>
+      </c>
+      <c r="AI41">
+        <v>2</v>
+      </c>
+      <c r="AJ41">
+        <v>2</v>
+      </c>
+      <c r="AK41">
+        <v>2</v>
+      </c>
+      <c r="AL41">
+        <v>1</v>
+      </c>
+      <c r="AM41">
+        <v>5</v>
+      </c>
+      <c r="AN41">
+        <v>2</v>
+      </c>
+      <c r="AO41">
+        <v>2</v>
+      </c>
+      <c r="AP41">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:27">
+    <row r="42" spans="1:42">
       <c r="A42" s="1">
         <v>0.05</v>
       </c>
@@ -4707,7 +5746,7 @@
       <c r="J42" s="1">
         <v>0.75</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="5">
         <v>0.2</v>
       </c>
       <c r="L42" s="1">
@@ -4738,7 +5777,7 @@
         <v>4</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="V42" s="1">
         <v>0.045</v>
@@ -4758,8 +5797,26 @@
       <c r="AA42" s="1">
         <v>0.1019</v>
       </c>
+      <c r="AK42">
+        <v>2</v>
+      </c>
+      <c r="AL42">
+        <v>2</v>
+      </c>
+      <c r="AM42">
+        <v>2</v>
+      </c>
+      <c r="AN42">
+        <v>2</v>
+      </c>
+      <c r="AO42">
+        <v>1</v>
+      </c>
+      <c r="AP42">
+        <v>5</v>
+      </c>
     </row>
-    <row r="43" spans="1:27">
+    <row r="43" spans="1:42">
       <c r="A43" s="1">
         <v>0.14</v>
       </c>
@@ -4790,7 +5847,7 @@
       <c r="J43" s="1">
         <v>0.75</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="5">
         <v>0.2</v>
       </c>
       <c r="L43" s="1">
@@ -4821,7 +5878,7 @@
         <v>6</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="V43" s="1">
         <v>0.09</v>
@@ -4841,8 +5898,26 @@
       <c r="AA43" s="1">
         <v>0.1768</v>
       </c>
+      <c r="AK43">
+        <v>2</v>
+      </c>
+      <c r="AL43">
+        <v>2</v>
+      </c>
+      <c r="AM43">
+        <v>2</v>
+      </c>
+      <c r="AN43">
+        <v>2</v>
+      </c>
+      <c r="AO43">
+        <v>5</v>
+      </c>
+      <c r="AP43">
+        <v>1</v>
+      </c>
     </row>
-    <row r="44" spans="1:27">
+    <row r="44" spans="1:42">
       <c r="A44" s="1">
         <v>0.13</v>
       </c>
@@ -4873,7 +5948,7 @@
       <c r="J44" s="1">
         <v>0.75</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="5">
         <v>0.2</v>
       </c>
       <c r="L44" s="1">
@@ -4904,7 +5979,7 @@
         <v>6</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="V44" s="1">
         <v>0.045</v>
@@ -4924,8 +5999,26 @@
       <c r="AA44" s="1">
         <v>0.1019</v>
       </c>
+      <c r="AK44">
+        <v>2</v>
+      </c>
+      <c r="AL44">
+        <v>2</v>
+      </c>
+      <c r="AM44">
+        <v>2</v>
+      </c>
+      <c r="AN44">
+        <v>2</v>
+      </c>
+      <c r="AO44">
+        <v>1</v>
+      </c>
+      <c r="AP44">
+        <v>5</v>
+      </c>
     </row>
-    <row r="45" spans="1:27">
+    <row r="45" spans="1:42">
       <c r="A45" s="1">
         <v>0.1</v>
       </c>
@@ -4956,7 +6049,7 @@
       <c r="J45" s="1">
         <v>0.75</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="5">
         <v>0.2</v>
       </c>
       <c r="L45" s="1">
@@ -4987,7 +6080,7 @@
         <v>60</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="V45" s="1">
         <v>0.022</v>
@@ -5007,8 +6100,26 @@
       <c r="AA45" s="1">
         <v>0.0645</v>
       </c>
+      <c r="AK45">
+        <v>2</v>
+      </c>
+      <c r="AL45">
+        <v>2</v>
+      </c>
+      <c r="AM45">
+        <v>2</v>
+      </c>
+      <c r="AN45">
+        <v>2</v>
+      </c>
+      <c r="AO45">
+        <v>1</v>
+      </c>
+      <c r="AP45">
+        <v>5</v>
+      </c>
     </row>
-    <row r="46" spans="1:27">
+    <row r="46" spans="1:42">
       <c r="A46" s="1">
         <v>0.18</v>
       </c>
@@ -5039,7 +6150,7 @@
       <c r="J46" s="1">
         <v>0.75</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="5">
         <v>0.2</v>
       </c>
       <c r="L46" s="1">
@@ -5070,7 +6181,7 @@
         <v>27</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="V46" s="1">
         <v>0.03</v>
@@ -5090,8 +6201,26 @@
       <c r="AA46" s="1">
         <v>0.0635</v>
       </c>
+      <c r="AK46">
+        <v>2</v>
+      </c>
+      <c r="AL46">
+        <v>2</v>
+      </c>
+      <c r="AM46">
+        <v>2</v>
+      </c>
+      <c r="AN46">
+        <v>2</v>
+      </c>
+      <c r="AO46">
+        <v>5</v>
+      </c>
+      <c r="AP46">
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:27">
+    <row r="47" spans="1:42">
       <c r="A47" s="1">
         <v>0.54</v>
       </c>
@@ -5122,7 +6251,7 @@
       <c r="J47" s="1">
         <v>0.75</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="5">
         <v>0.2</v>
       </c>
       <c r="L47" s="1">
@@ -5153,7 +6282,7 @@
         <v>6</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="V47" s="1">
         <v>0.09</v>
@@ -5173,8 +6302,26 @@
       <c r="AA47" s="1">
         <v>0.3118</v>
       </c>
+      <c r="AK47">
+        <v>2</v>
+      </c>
+      <c r="AL47">
+        <v>2</v>
+      </c>
+      <c r="AM47">
+        <v>2</v>
+      </c>
+      <c r="AN47">
+        <v>2</v>
+      </c>
+      <c r="AO47">
+        <v>5</v>
+      </c>
+      <c r="AP47">
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:27">
+    <row r="48" spans="1:42">
       <c r="A48" s="1">
         <v>0.74</v>
       </c>
@@ -5205,7 +6352,7 @@
       <c r="J48" s="1">
         <v>0.75</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="5">
         <v>0.2</v>
       </c>
       <c r="L48" s="1">
@@ -5236,7 +6383,7 @@
         <v>7</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="V48" s="1">
         <v>0.03</v>
@@ -5256,8 +6403,26 @@
       <c r="AA48" s="1">
         <v>0.0635</v>
       </c>
+      <c r="AK48">
+        <v>2</v>
+      </c>
+      <c r="AL48">
+        <v>2</v>
+      </c>
+      <c r="AM48">
+        <v>2</v>
+      </c>
+      <c r="AN48">
+        <v>2</v>
+      </c>
+      <c r="AO48">
+        <v>1</v>
+      </c>
+      <c r="AP48">
+        <v>5</v>
+      </c>
     </row>
-    <row r="49" spans="1:27">
+    <row r="49" spans="1:42">
       <c r="A49" s="1">
         <v>0.09</v>
       </c>
@@ -5288,7 +6453,7 @@
       <c r="J49" s="1">
         <v>0.75</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="5">
         <v>0.2</v>
       </c>
       <c r="L49" s="1">
@@ -5319,7 +6484,7 @@
         <v>17</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="V49" s="1">
         <v>0.022</v>
@@ -5339,8 +6504,26 @@
       <c r="AA49" s="1">
         <v>0.078</v>
       </c>
+      <c r="AK49">
+        <v>2</v>
+      </c>
+      <c r="AL49">
+        <v>2</v>
+      </c>
+      <c r="AM49">
+        <v>2</v>
+      </c>
+      <c r="AN49">
+        <v>2</v>
+      </c>
+      <c r="AO49">
+        <v>5</v>
+      </c>
+      <c r="AP49">
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:27">
+    <row r="50" spans="1:42">
       <c r="A50" s="1">
         <v>0.15</v>
       </c>
@@ -5371,7 +6554,7 @@
       <c r="J50" s="1">
         <v>0.75</v>
       </c>
-      <c r="K50" s="3">
+      <c r="K50" s="5">
         <v>0.2</v>
       </c>
       <c r="L50" s="1">
@@ -5402,7 +6585,7 @@
         <v>7</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="V50" s="1">
         <v>0.022</v>
@@ -5422,8 +6605,26 @@
       <c r="AA50" s="1">
         <v>0.051</v>
       </c>
+      <c r="AK50">
+        <v>2</v>
+      </c>
+      <c r="AL50">
+        <v>2</v>
+      </c>
+      <c r="AM50">
+        <v>2</v>
+      </c>
+      <c r="AN50">
+        <v>2</v>
+      </c>
+      <c r="AO50">
+        <v>1</v>
+      </c>
+      <c r="AP50">
+        <v>5</v>
+      </c>
     </row>
-    <row r="51" spans="1:27">
+    <row r="51" spans="1:42">
       <c r="A51" s="1">
         <v>0.87</v>
       </c>
@@ -5454,7 +6655,7 @@
       <c r="J51" s="1">
         <v>0.75</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K51" s="5">
         <v>0.2</v>
       </c>
       <c r="L51" s="1">
@@ -5485,7 +6686,7 @@
         <v>17</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="V51" s="1">
         <v>0.018</v>
@@ -5505,8 +6706,26 @@
       <c r="AA51" s="1">
         <v>0.0448</v>
       </c>
+      <c r="AK51">
+        <v>2</v>
+      </c>
+      <c r="AL51">
+        <v>2</v>
+      </c>
+      <c r="AM51">
+        <v>2</v>
+      </c>
+      <c r="AN51">
+        <v>2</v>
+      </c>
+      <c r="AO51">
+        <v>5</v>
+      </c>
+      <c r="AP51">
+        <v>1</v>
+      </c>
     </row>
-    <row r="52" spans="1:27">
+    <row r="52" spans="1:42">
       <c r="A52" s="1">
         <v>0.04</v>
       </c>
@@ -5537,7 +6756,7 @@
       <c r="J52" s="1">
         <v>0.75</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="5">
         <v>0.2</v>
       </c>
       <c r="L52" s="1">
@@ -5568,7 +6787,7 @@
         <v>26</v>
       </c>
       <c r="U52" s="1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="V52" s="1">
         <v>0.015</v>
@@ -5588,8 +6807,26 @@
       <c r="AA52" s="1">
         <v>0.0385</v>
       </c>
+      <c r="AK52">
+        <v>2</v>
+      </c>
+      <c r="AL52">
+        <v>2</v>
+      </c>
+      <c r="AM52">
+        <v>2</v>
+      </c>
+      <c r="AN52">
+        <v>2</v>
+      </c>
+      <c r="AO52">
+        <v>1</v>
+      </c>
+      <c r="AP52">
+        <v>5</v>
+      </c>
     </row>
-    <row r="53" spans="1:27">
+    <row r="53" spans="1:42">
       <c r="A53" s="1">
         <v>0.76</v>
       </c>
@@ -5620,7 +6857,7 @@
       <c r="J53" s="1">
         <v>0.75</v>
       </c>
-      <c r="K53" s="3">
+      <c r="K53" s="5">
         <v>0.2</v>
       </c>
       <c r="L53" s="1">
@@ -5651,7 +6888,7 @@
         <v>47</v>
       </c>
       <c r="U53" s="1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="V53" s="1">
         <v>0.022</v>
@@ -5671,8 +6908,26 @@
       <c r="AA53" s="1">
         <v>0.0375</v>
       </c>
+      <c r="AK53">
+        <v>2</v>
+      </c>
+      <c r="AL53">
+        <v>2</v>
+      </c>
+      <c r="AM53">
+        <v>2</v>
+      </c>
+      <c r="AN53">
+        <v>2</v>
+      </c>
+      <c r="AO53">
+        <v>5</v>
+      </c>
+      <c r="AP53">
+        <v>1</v>
+      </c>
     </row>
-    <row r="54" spans="1:27">
+    <row r="54" spans="1:42">
       <c r="A54" s="1">
         <v>0.83</v>
       </c>
@@ -5703,7 +6958,7 @@
       <c r="J54" s="1">
         <v>0.2</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="5">
         <v>0.6</v>
       </c>
       <c r="L54" s="1">
@@ -5733,8 +6988,8 @@
       <c r="T54" s="1">
         <v>10</v>
       </c>
-      <c r="U54" s="1" t="s">
-        <v>79</v>
+      <c r="U54" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="V54" s="1">
         <v>0.3</v>
@@ -5754,8 +7009,35 @@
       <c r="AA54" s="1">
         <v>0.9045</v>
       </c>
+      <c r="AH54">
+        <v>2</v>
+      </c>
+      <c r="AI54">
+        <v>2</v>
+      </c>
+      <c r="AJ54">
+        <v>2</v>
+      </c>
+      <c r="AK54">
+        <v>2</v>
+      </c>
+      <c r="AL54">
+        <v>5</v>
+      </c>
+      <c r="AM54">
+        <v>1</v>
+      </c>
+      <c r="AN54">
+        <v>2</v>
+      </c>
+      <c r="AO54">
+        <v>2</v>
+      </c>
+      <c r="AP54">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:27">
+    <row r="55" spans="1:42">
       <c r="A55" s="1">
         <v>0.15</v>
       </c>
@@ -5786,7 +7068,7 @@
       <c r="J55" s="1">
         <v>0.75</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K55" s="5">
         <v>0.2</v>
       </c>
       <c r="L55" s="1">
@@ -5817,7 +7099,7 @@
         <v>70</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="V55" s="1">
         <v>0.015</v>
@@ -5837,8 +7119,26 @@
       <c r="AA55" s="1">
         <v>0.0385</v>
       </c>
+      <c r="AK55">
+        <v>2</v>
+      </c>
+      <c r="AL55">
+        <v>2</v>
+      </c>
+      <c r="AM55">
+        <v>2</v>
+      </c>
+      <c r="AN55">
+        <v>2</v>
+      </c>
+      <c r="AO55">
+        <v>1</v>
+      </c>
+      <c r="AP55">
+        <v>5</v>
+      </c>
     </row>
-    <row r="56" spans="1:27">
+    <row r="56" spans="1:42">
       <c r="A56" s="1">
         <v>0.13</v>
       </c>
@@ -5869,7 +7169,7 @@
       <c r="J56" s="1">
         <v>0.75</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K56" s="5">
         <v>0.2</v>
       </c>
       <c r="L56" s="1">
@@ -5900,7 +7200,7 @@
         <v>7</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="V56" s="1">
         <v>0.015</v>
@@ -5920,8 +7220,26 @@
       <c r="AA56" s="1">
         <v>0.0385</v>
       </c>
+      <c r="AK56">
+        <v>2</v>
+      </c>
+      <c r="AL56">
+        <v>2</v>
+      </c>
+      <c r="AM56">
+        <v>2</v>
+      </c>
+      <c r="AN56">
+        <v>2</v>
+      </c>
+      <c r="AO56">
+        <v>5</v>
+      </c>
+      <c r="AP56">
+        <v>1</v>
+      </c>
     </row>
-    <row r="57" spans="1:27">
+    <row r="57" spans="1:42">
       <c r="A57" s="1">
         <v>0.81</v>
       </c>
@@ -5952,7 +7270,7 @@
       <c r="J57" s="1">
         <v>0.75</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="5">
         <v>0.2</v>
       </c>
       <c r="L57" s="1">
@@ -5983,7 +7301,7 @@
         <v>60</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="V57" s="1">
         <v>0.003</v>
@@ -6003,8 +7321,26 @@
       <c r="AA57" s="1">
         <v>0.009</v>
       </c>
+      <c r="AK57">
+        <v>2</v>
+      </c>
+      <c r="AL57">
+        <v>2</v>
+      </c>
+      <c r="AM57">
+        <v>2</v>
+      </c>
+      <c r="AN57">
+        <v>2</v>
+      </c>
+      <c r="AO57">
+        <v>1</v>
+      </c>
+      <c r="AP57">
+        <v>5</v>
+      </c>
     </row>
-    <row r="58" spans="1:27">
+    <row r="58" spans="1:42">
       <c r="A58" s="1">
         <v>0.82</v>
       </c>
@@ -6035,7 +7371,7 @@
       <c r="J58" s="1">
         <v>0.75</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="5">
         <v>0.2</v>
       </c>
       <c r="L58" s="1">
@@ -6066,7 +7402,7 @@
         <v>14</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="V58" s="1">
         <v>0.003</v>
@@ -6086,8 +7422,26 @@
       <c r="AA58" s="1">
         <v>0.0333</v>
       </c>
+      <c r="AK58">
+        <v>2</v>
+      </c>
+      <c r="AL58">
+        <v>2</v>
+      </c>
+      <c r="AM58">
+        <v>2</v>
+      </c>
+      <c r="AN58">
+        <v>2</v>
+      </c>
+      <c r="AO58">
+        <v>1</v>
+      </c>
+      <c r="AP58">
+        <v>5</v>
+      </c>
     </row>
-    <row r="59" spans="1:27">
+    <row r="59" spans="1:42">
       <c r="A59" s="1">
         <v>0.22</v>
       </c>
@@ -6118,7 +7472,7 @@
       <c r="J59" s="1">
         <v>0.75</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="5">
         <v>0.2</v>
       </c>
       <c r="L59" s="1">
@@ -6149,7 +7503,7 @@
         <v>20</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="V59" s="1">
         <v>0.003</v>
@@ -6169,8 +7523,26 @@
       <c r="AA59" s="1">
         <v>0.009</v>
       </c>
+      <c r="AK59">
+        <v>2</v>
+      </c>
+      <c r="AL59">
+        <v>2</v>
+      </c>
+      <c r="AM59">
+        <v>2</v>
+      </c>
+      <c r="AN59">
+        <v>2</v>
+      </c>
+      <c r="AO59">
+        <v>1</v>
+      </c>
+      <c r="AP59">
+        <v>5</v>
+      </c>
     </row>
-    <row r="60" spans="1:27">
+    <row r="60" spans="1:42">
       <c r="A60" s="1">
         <v>0.12</v>
       </c>
@@ -6201,7 +7573,7 @@
       <c r="J60" s="1">
         <v>0.75</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="5">
         <v>0.2</v>
       </c>
       <c r="L60" s="1">
@@ -6232,7 +7604,7 @@
         <v>6</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="V60" s="1">
         <v>0.012</v>
@@ -6252,8 +7624,26 @@
       <c r="AA60" s="1">
         <v>0.0186</v>
       </c>
+      <c r="AK60">
+        <v>2</v>
+      </c>
+      <c r="AL60">
+        <v>2</v>
+      </c>
+      <c r="AM60">
+        <v>2</v>
+      </c>
+      <c r="AN60">
+        <v>2</v>
+      </c>
+      <c r="AO60">
+        <v>1</v>
+      </c>
+      <c r="AP60">
+        <v>5</v>
+      </c>
     </row>
-    <row r="61" spans="1:27">
+    <row r="61" spans="1:42">
       <c r="A61" s="1">
         <v>0</v>
       </c>
@@ -6284,7 +7674,7 @@
       <c r="J61" s="1">
         <v>0.75</v>
       </c>
-      <c r="K61" s="3">
+      <c r="K61" s="5">
         <v>0.2</v>
       </c>
       <c r="L61" s="1">
@@ -6315,7 +7705,7 @@
         <v>6</v>
       </c>
       <c r="U61" s="1" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="V61" s="1">
         <v>0.012</v>
@@ -6335,8 +7725,26 @@
       <c r="AA61" s="1">
         <v>0.0186</v>
       </c>
+      <c r="AK61">
+        <v>2</v>
+      </c>
+      <c r="AL61">
+        <v>2</v>
+      </c>
+      <c r="AM61">
+        <v>2</v>
+      </c>
+      <c r="AN61">
+        <v>2</v>
+      </c>
+      <c r="AO61">
+        <v>5</v>
+      </c>
+      <c r="AP61">
+        <v>1</v>
+      </c>
     </row>
-    <row r="62" spans="1:27">
+    <row r="62" spans="1:42">
       <c r="A62" s="1">
         <v>0.78</v>
       </c>
@@ -6367,7 +7775,7 @@
       <c r="J62" s="1">
         <v>0.75</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="5">
         <v>0.2</v>
       </c>
       <c r="L62" s="1">
@@ -6398,7 +7806,7 @@
         <v>26</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="V62" s="1">
         <v>0.007</v>
@@ -6418,8 +7826,26 @@
       <c r="AA62" s="1">
         <v>0.0193</v>
       </c>
+      <c r="AK62">
+        <v>2</v>
+      </c>
+      <c r="AL62">
+        <v>2</v>
+      </c>
+      <c r="AM62">
+        <v>2</v>
+      </c>
+      <c r="AN62">
+        <v>2</v>
+      </c>
+      <c r="AO62">
+        <v>1</v>
+      </c>
+      <c r="AP62">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="1:27">
+    <row r="63" spans="1:42">
       <c r="A63" s="1">
         <v>0.89</v>
       </c>
@@ -6450,7 +7876,7 @@
       <c r="J63" s="1">
         <v>0.75</v>
       </c>
-      <c r="K63" s="3">
+      <c r="K63" s="5">
         <v>0.2</v>
       </c>
       <c r="L63" s="1">
@@ -6481,7 +7907,7 @@
         <v>12</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="V63" s="1">
         <v>0.004</v>
@@ -6501,8 +7927,26 @@
       <c r="AA63" s="1">
         <v>0.013</v>
       </c>
+      <c r="AK63">
+        <v>2</v>
+      </c>
+      <c r="AL63">
+        <v>2</v>
+      </c>
+      <c r="AM63">
+        <v>2</v>
+      </c>
+      <c r="AN63">
+        <v>2</v>
+      </c>
+      <c r="AO63">
+        <v>1</v>
+      </c>
+      <c r="AP63">
+        <v>5</v>
+      </c>
     </row>
-    <row r="64" spans="1:27">
+    <row r="64" spans="1:42">
       <c r="A64" s="1">
         <v>0.04</v>
       </c>
@@ -6533,7 +7977,7 @@
       <c r="J64" s="1">
         <v>0.75</v>
       </c>
-      <c r="K64" s="3">
+      <c r="K64" s="5">
         <v>0.2</v>
       </c>
       <c r="L64" s="1">
@@ -6564,7 +8008,7 @@
         <v>6</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="V64" s="1">
         <v>0.007</v>
@@ -6584,8 +8028,26 @@
       <c r="AA64" s="1">
         <v>0.0126</v>
       </c>
+      <c r="AK64">
+        <v>2</v>
+      </c>
+      <c r="AL64">
+        <v>2</v>
+      </c>
+      <c r="AM64">
+        <v>2</v>
+      </c>
+      <c r="AN64">
+        <v>2</v>
+      </c>
+      <c r="AO64">
+        <v>1</v>
+      </c>
+      <c r="AP64">
+        <v>5</v>
+      </c>
     </row>
-    <row r="65" spans="1:27">
+    <row r="65" spans="1:42">
       <c r="A65" s="1">
         <v>0.05</v>
       </c>
@@ -6616,7 +8078,7 @@
       <c r="J65" s="1">
         <v>0.75</v>
       </c>
-      <c r="K65" s="3">
+      <c r="K65" s="5">
         <v>0.2</v>
       </c>
       <c r="L65" s="1">
@@ -6647,7 +8109,7 @@
         <v>16</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="V65" s="1">
         <v>0.006</v>
@@ -6667,8 +8129,26 @@
       <c r="AA65" s="1">
         <v>0.0194</v>
       </c>
+      <c r="AK65">
+        <v>2</v>
+      </c>
+      <c r="AL65">
+        <v>2</v>
+      </c>
+      <c r="AM65">
+        <v>2</v>
+      </c>
+      <c r="AN65">
+        <v>2</v>
+      </c>
+      <c r="AO65">
+        <v>5</v>
+      </c>
+      <c r="AP65">
+        <v>1</v>
+      </c>
     </row>
-    <row r="66" spans="1:27">
+    <row r="66" spans="1:42">
       <c r="A66" s="1">
         <v>0.13</v>
       </c>
@@ -6699,7 +8179,7 @@
       <c r="J66" s="1">
         <v>0.75</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="5">
         <v>0.2</v>
       </c>
       <c r="L66" s="1">
@@ -6730,7 +8210,7 @@
         <v>6</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="V66" s="1">
         <v>0.003</v>
@@ -6750,8 +8230,26 @@
       <c r="AA66" s="1">
         <v>0.009</v>
       </c>
+      <c r="AK66">
+        <v>2</v>
+      </c>
+      <c r="AL66">
+        <v>2</v>
+      </c>
+      <c r="AM66">
+        <v>2</v>
+      </c>
+      <c r="AN66">
+        <v>2</v>
+      </c>
+      <c r="AO66">
+        <v>1</v>
+      </c>
+      <c r="AP66">
+        <v>5</v>
+      </c>
     </row>
-    <row r="67" spans="1:27">
+    <row r="67" spans="1:42">
       <c r="A67" s="1">
         <v>0</v>
       </c>
@@ -6767,7 +8265,7 @@
       <c r="E67" s="1">
         <v>0.72</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67" s="5">
         <v>0</v>
       </c>
       <c r="G67" s="1">
@@ -6782,7 +8280,7 @@
       <c r="J67" s="1">
         <v>0.2</v>
       </c>
-      <c r="K67" s="3">
+      <c r="K67" s="5">
         <v>0.6</v>
       </c>
       <c r="L67" s="1">
@@ -6812,8 +8310,8 @@
       <c r="T67" s="1">
         <v>270</v>
       </c>
-      <c r="U67" s="1" t="s">
-        <v>92</v>
+      <c r="U67" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="V67" s="1">
         <v>0.3</v>
@@ -6833,8 +8331,35 @@
       <c r="AA67" s="1">
         <v>0.7695</v>
       </c>
+      <c r="AH67">
+        <v>2</v>
+      </c>
+      <c r="AI67">
+        <v>2</v>
+      </c>
+      <c r="AJ67">
+        <v>2</v>
+      </c>
+      <c r="AK67">
+        <v>2</v>
+      </c>
+      <c r="AL67">
+        <v>1</v>
+      </c>
+      <c r="AM67">
+        <v>5</v>
+      </c>
+      <c r="AN67">
+        <v>2</v>
+      </c>
+      <c r="AO67">
+        <v>2</v>
+      </c>
+      <c r="AP67">
+        <v>2</v>
+      </c>
     </row>
-    <row r="68" spans="1:27">
+    <row r="68" spans="1:42">
       <c r="A68" s="1">
         <v>0.06</v>
       </c>
@@ -6865,7 +8390,7 @@
       <c r="J68" s="1">
         <v>0.75</v>
       </c>
-      <c r="K68" s="3">
+      <c r="K68" s="5">
         <v>0.2</v>
       </c>
       <c r="L68" s="1">
@@ -6896,7 +8421,7 @@
         <v>270</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="V68" s="1">
         <v>0.003</v>
@@ -6915,6 +8440,24 @@
       </c>
       <c r="AA68" s="1">
         <v>0.009</v>
+      </c>
+      <c r="AK68">
+        <v>2</v>
+      </c>
+      <c r="AL68">
+        <v>2</v>
+      </c>
+      <c r="AM68">
+        <v>2</v>
+      </c>
+      <c r="AN68">
+        <v>2</v>
+      </c>
+      <c r="AO68">
+        <v>1</v>
+      </c>
+      <c r="AP68">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/price.xlsx
+++ b/price.xlsx
@@ -4192,6 +4192,33 @@
       <c r="AA27" s="1">
         <v>2.6494</v>
       </c>
+      <c r="AE27">
+        <v>2</v>
+      </c>
+      <c r="AF27">
+        <v>2</v>
+      </c>
+      <c r="AG27">
+        <v>2</v>
+      </c>
+      <c r="AH27">
+        <v>2</v>
+      </c>
+      <c r="AI27">
+        <v>1</v>
+      </c>
+      <c r="AJ27">
+        <v>5</v>
+      </c>
+      <c r="AK27">
+        <v>2</v>
+      </c>
+      <c r="AL27">
+        <v>2</v>
+      </c>
+      <c r="AM27">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:42">
       <c r="A28" s="1">

--- a/price.xlsx
+++ b/price.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>浅海</t>
   </si>
@@ -1346,10 +1346,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AP68"/>
+  <dimension ref="A1:AQ68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:43">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1476,8 +1476,11 @@
       <c r="AP1" t="s">
         <v>41</v>
       </c>
+      <c r="AQ1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:42">
+    <row r="2" spans="1:43">
       <c r="A2" s="1">
         <v>0.03</v>
       </c>
@@ -1577,8 +1580,11 @@
       <c r="AG2">
         <v>2</v>
       </c>
+      <c r="AQ2">
+        <v>2</v>
+      </c>
     </row>
-    <row r="3" spans="1:42">
+    <row r="3" spans="1:43">
       <c r="A3" s="1">
         <v>0.02</v>
       </c>
@@ -1678,8 +1684,11 @@
       <c r="AG3">
         <v>2</v>
       </c>
+      <c r="AQ3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:43">
       <c r="A4" s="1">
         <v>0.09</v>
       </c>
@@ -1779,8 +1788,11 @@
       <c r="AG4">
         <v>2</v>
       </c>
+      <c r="AQ4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:42">
+    <row r="5" spans="1:43">
       <c r="A5" s="1">
         <v>0.1</v>
       </c>
@@ -1880,8 +1892,11 @@
       <c r="AG5">
         <v>2</v>
       </c>
+      <c r="AQ5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:43">
       <c r="A6" s="1">
         <v>0.08</v>
       </c>
@@ -1981,8 +1996,11 @@
       <c r="AG6">
         <v>2</v>
       </c>
+      <c r="AQ6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:42">
+    <row r="7" spans="1:43">
       <c r="A7" s="1">
         <v>0.08</v>
       </c>
@@ -2082,8 +2100,11 @@
       <c r="AG7">
         <v>2</v>
       </c>
+      <c r="AQ7">
+        <v>2</v>
+      </c>
     </row>
-    <row r="8" spans="1:42">
+    <row r="8" spans="1:43">
       <c r="A8" s="1">
         <v>0.15</v>
       </c>
@@ -2183,8 +2204,11 @@
       <c r="AG8">
         <v>2</v>
       </c>
+      <c r="AQ8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:42">
+    <row r="9" spans="1:43">
       <c r="A9" s="1">
         <v>0.03</v>
       </c>
@@ -2284,8 +2308,11 @@
       <c r="AG9">
         <v>2</v>
       </c>
+      <c r="AQ9">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:42">
+    <row r="10" spans="1:43">
       <c r="A10" s="1">
         <v>0.04</v>
       </c>
@@ -2385,8 +2412,11 @@
       <c r="AG10">
         <v>2</v>
       </c>
+      <c r="AQ10">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:42">
+    <row r="11" spans="1:43">
       <c r="A11" s="1">
         <v>0.68</v>
       </c>
@@ -2486,8 +2516,11 @@
       <c r="AG11">
         <v>2</v>
       </c>
+      <c r="AQ11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:42">
+    <row r="12" spans="1:43">
       <c r="A12" s="1">
         <v>0.03</v>
       </c>
@@ -2587,8 +2620,11 @@
       <c r="AG12">
         <v>2</v>
       </c>
+      <c r="AQ12">
+        <v>1</v>
+      </c>
     </row>
-    <row r="13" spans="1:42">
+    <row r="13" spans="1:43">
       <c r="A13" s="1">
         <v>0.07</v>
       </c>
@@ -2688,8 +2724,11 @@
       <c r="AG13">
         <v>2</v>
       </c>
+      <c r="AQ13">
+        <v>3</v>
+      </c>
     </row>
-    <row r="14" spans="1:42">
+    <row r="14" spans="1:43">
       <c r="A14" s="1">
         <v>0.1</v>
       </c>
@@ -2798,8 +2837,11 @@
       <c r="AJ14">
         <v>2</v>
       </c>
+      <c r="AQ14">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:42">
+    <row r="15" spans="1:43">
       <c r="A15" s="1">
         <v>0.01</v>
       </c>
@@ -2908,8 +2950,11 @@
       <c r="AJ15">
         <v>2</v>
       </c>
+      <c r="AQ15">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:42">
+    <row r="16" spans="1:43">
       <c r="A16" s="1">
         <v>0.05</v>
       </c>
@@ -3018,8 +3063,11 @@
       <c r="AJ16">
         <v>2</v>
       </c>
+      <c r="AQ16">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:42">
+    <row r="17" spans="1:43">
       <c r="A17" s="1">
         <v>0.05</v>
       </c>
@@ -3128,8 +3176,11 @@
       <c r="AJ17">
         <v>2</v>
       </c>
+      <c r="AQ17">
+        <v>1</v>
+      </c>
     </row>
-    <row r="18" spans="1:42">
+    <row r="18" spans="1:43">
       <c r="A18" s="1">
         <v>0.08</v>
       </c>
@@ -3238,8 +3289,11 @@
       <c r="AJ18">
         <v>2</v>
       </c>
+      <c r="AQ18">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:42">
+    <row r="19" spans="1:43">
       <c r="A19" s="1">
         <v>0.06</v>
       </c>
@@ -3348,8 +3402,11 @@
       <c r="AJ19">
         <v>2</v>
       </c>
+      <c r="AQ19">
+        <v>2</v>
+      </c>
     </row>
-    <row r="20" spans="1:42">
+    <row r="20" spans="1:43">
       <c r="A20" s="1">
         <v>0.13</v>
       </c>
@@ -3449,8 +3506,11 @@
       <c r="AP20">
         <v>1</v>
       </c>
+      <c r="AQ20">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:42">
+    <row r="21" spans="1:43">
       <c r="A21" s="1">
         <v>0.17</v>
       </c>
@@ -3559,8 +3619,11 @@
       <c r="AP21">
         <v>2</v>
       </c>
+      <c r="AQ21">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:42">
+    <row r="22" spans="1:43">
       <c r="A22" s="1">
         <v>0.04</v>
       </c>
@@ -3669,8 +3732,11 @@
       <c r="AM22">
         <v>2</v>
       </c>
+      <c r="AQ22">
+        <v>2</v>
+      </c>
     </row>
-    <row r="23" spans="1:42">
+    <row r="23" spans="1:43">
       <c r="A23" s="1">
         <v>0.08</v>
       </c>
@@ -3779,8 +3845,11 @@
       <c r="AM23">
         <v>2</v>
       </c>
+      <c r="AQ23">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="1:42">
+    <row r="24" spans="1:43">
       <c r="A24" s="1">
         <v>0.13</v>
       </c>
@@ -3889,8 +3958,11 @@
       <c r="AM24">
         <v>2</v>
       </c>
+      <c r="AQ24">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:42">
+    <row r="25" spans="1:43">
       <c r="A25" s="1">
         <v>0.88</v>
       </c>
@@ -3999,8 +4071,11 @@
       <c r="AJ25">
         <v>2</v>
       </c>
+      <c r="AQ25">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:42">
+    <row r="26" spans="1:43">
       <c r="A26" s="1">
         <v>0.07</v>
       </c>
@@ -4109,8 +4184,11 @@
       <c r="AP26">
         <v>2</v>
       </c>
+      <c r="AQ26">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:42">
+    <row r="27" spans="1:43">
       <c r="A27" s="1">
         <v>0.1</v>
       </c>
@@ -4219,8 +4297,11 @@
       <c r="AM27">
         <v>2</v>
       </c>
+      <c r="AQ27">
+        <v>1</v>
+      </c>
     </row>
-    <row r="28" spans="1:42">
+    <row r="28" spans="1:43">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -4329,8 +4410,11 @@
       <c r="AP28">
         <v>2</v>
       </c>
+      <c r="AQ28">
+        <v>2</v>
+      </c>
     </row>
-    <row r="29" spans="1:42">
+    <row r="29" spans="1:43">
       <c r="A29" s="1">
         <v>0.15</v>
       </c>
@@ -4439,8 +4523,11 @@
       <c r="AJ29">
         <v>2</v>
       </c>
+      <c r="AQ29">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:42">
+    <row r="30" spans="1:43">
       <c r="A30" s="1">
         <v>0.09</v>
       </c>
@@ -4540,8 +4627,11 @@
       <c r="AP30">
         <v>5</v>
       </c>
+      <c r="AQ30">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:42">
+    <row r="31" spans="1:43">
       <c r="A31" s="1">
         <v>0.06</v>
       </c>
@@ -4650,8 +4740,11 @@
       <c r="AP31">
         <v>2</v>
       </c>
+      <c r="AQ31">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:42">
+    <row r="32" spans="1:43">
       <c r="A32" s="1">
         <v>0.07</v>
       </c>
@@ -4760,8 +4853,11 @@
       <c r="AM32">
         <v>2</v>
       </c>
+      <c r="AQ32">
+        <v>2</v>
+      </c>
     </row>
-    <row r="33" spans="1:42">
+    <row r="33" spans="1:43">
       <c r="A33" s="1">
         <v>0.77</v>
       </c>
@@ -4870,8 +4966,11 @@
       <c r="AP33">
         <v>2</v>
       </c>
+      <c r="AQ33">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:42">
+    <row r="34" spans="1:43">
       <c r="A34" s="1">
         <v>0.03</v>
       </c>
@@ -4980,8 +5079,11 @@
       <c r="AP34">
         <v>2</v>
       </c>
+      <c r="AQ34">
+        <v>3</v>
+      </c>
     </row>
-    <row r="35" spans="1:42">
+    <row r="35" spans="1:43">
       <c r="A35" s="1">
         <v>0.15</v>
       </c>
@@ -5090,8 +5192,11 @@
       <c r="AM35">
         <v>2</v>
       </c>
+      <c r="AQ35">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:42">
+    <row r="36" spans="1:43">
       <c r="A36" s="1">
         <v>0.07</v>
       </c>
@@ -5200,8 +5305,11 @@
       <c r="AM36">
         <v>2</v>
       </c>
+      <c r="AQ36">
+        <v>1</v>
+      </c>
     </row>
-    <row r="37" spans="1:42">
+    <row r="37" spans="1:43">
       <c r="A37" s="1">
         <v>0.11</v>
       </c>
@@ -5310,8 +5418,11 @@
       <c r="AP37">
         <v>2</v>
       </c>
+      <c r="AQ37">
+        <v>3</v>
+      </c>
     </row>
-    <row r="38" spans="1:42">
+    <row r="38" spans="1:43">
       <c r="A38" s="1">
         <v>0.07</v>
       </c>
@@ -5411,8 +5522,11 @@
       <c r="AP38">
         <v>5</v>
       </c>
+      <c r="AQ38">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="1:42">
+    <row r="39" spans="1:43">
       <c r="A39" s="1">
         <v>0.05</v>
       </c>
@@ -5521,8 +5635,11 @@
       <c r="AP39">
         <v>2</v>
       </c>
+      <c r="AQ39">
+        <v>1</v>
+      </c>
     </row>
-    <row r="40" spans="1:42">
+    <row r="40" spans="1:43">
       <c r="A40" s="1">
         <v>0.18</v>
       </c>
@@ -5631,8 +5748,11 @@
       <c r="AM40">
         <v>2</v>
       </c>
+      <c r="AQ40">
+        <v>3</v>
+      </c>
     </row>
-    <row r="41" spans="1:42">
+    <row r="41" spans="1:43">
       <c r="A41" s="1">
         <v>0.03</v>
       </c>
@@ -5741,8 +5861,11 @@
       <c r="AP41">
         <v>2</v>
       </c>
+      <c r="AQ41">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="1:42">
+    <row r="42" spans="1:43">
       <c r="A42" s="1">
         <v>0.05</v>
       </c>
@@ -5842,8 +5965,11 @@
       <c r="AP42">
         <v>5</v>
       </c>
+      <c r="AQ42">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="1:42">
+    <row r="43" spans="1:43">
       <c r="A43" s="1">
         <v>0.14</v>
       </c>
@@ -5943,8 +6069,11 @@
       <c r="AP43">
         <v>1</v>
       </c>
+      <c r="AQ43">
+        <v>3</v>
+      </c>
     </row>
-    <row r="44" spans="1:42">
+    <row r="44" spans="1:43">
       <c r="A44" s="1">
         <v>0.13</v>
       </c>
@@ -6044,8 +6173,11 @@
       <c r="AP44">
         <v>5</v>
       </c>
+      <c r="AQ44">
+        <v>3</v>
+      </c>
     </row>
-    <row r="45" spans="1:42">
+    <row r="45" spans="1:43">
       <c r="A45" s="1">
         <v>0.1</v>
       </c>
@@ -6145,8 +6277,11 @@
       <c r="AP45">
         <v>5</v>
       </c>
+      <c r="AQ45">
+        <v>2</v>
+      </c>
     </row>
-    <row r="46" spans="1:42">
+    <row r="46" spans="1:43">
       <c r="A46" s="1">
         <v>0.18</v>
       </c>
@@ -6246,8 +6381,11 @@
       <c r="AP46">
         <v>1</v>
       </c>
+      <c r="AQ46">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="1:42">
+    <row r="47" spans="1:43">
       <c r="A47" s="1">
         <v>0.54</v>
       </c>
@@ -6347,8 +6485,11 @@
       <c r="AP47">
         <v>1</v>
       </c>
+      <c r="AQ47">
+        <v>3</v>
+      </c>
     </row>
-    <row r="48" spans="1:42">
+    <row r="48" spans="1:43">
       <c r="A48" s="1">
         <v>0.74</v>
       </c>
@@ -6448,8 +6589,11 @@
       <c r="AP48">
         <v>5</v>
       </c>
+      <c r="AQ48">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="1:42">
+    <row r="49" spans="1:43">
       <c r="A49" s="1">
         <v>0.09</v>
       </c>
@@ -6549,8 +6693,11 @@
       <c r="AP49">
         <v>1</v>
       </c>
+      <c r="AQ49">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:42">
+    <row r="50" spans="1:43">
       <c r="A50" s="1">
         <v>0.15</v>
       </c>
@@ -6650,8 +6797,11 @@
       <c r="AP50">
         <v>5</v>
       </c>
+      <c r="AQ50">
+        <v>3</v>
+      </c>
     </row>
-    <row r="51" spans="1:42">
+    <row r="51" spans="1:43">
       <c r="A51" s="1">
         <v>0.87</v>
       </c>
@@ -6751,8 +6901,11 @@
       <c r="AP51">
         <v>1</v>
       </c>
+      <c r="AQ51">
+        <v>3</v>
+      </c>
     </row>
-    <row r="52" spans="1:42">
+    <row r="52" spans="1:43">
       <c r="A52" s="1">
         <v>0.04</v>
       </c>
@@ -6852,8 +7005,11 @@
       <c r="AP52">
         <v>5</v>
       </c>
+      <c r="AQ52">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:42">
+    <row r="53" spans="1:43">
       <c r="A53" s="1">
         <v>0.76</v>
       </c>
@@ -6953,8 +7109,11 @@
       <c r="AP53">
         <v>1</v>
       </c>
+      <c r="AQ53">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:42">
+    <row r="54" spans="1:43">
       <c r="A54" s="1">
         <v>0.83</v>
       </c>
@@ -7063,8 +7222,11 @@
       <c r="AP54">
         <v>2</v>
       </c>
+      <c r="AQ54">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="1:42">
+    <row r="55" spans="1:43">
       <c r="A55" s="1">
         <v>0.15</v>
       </c>
@@ -7164,8 +7326,11 @@
       <c r="AP55">
         <v>5</v>
       </c>
+      <c r="AQ55">
+        <v>1</v>
+      </c>
     </row>
-    <row r="56" spans="1:42">
+    <row r="56" spans="1:43">
       <c r="A56" s="1">
         <v>0.13</v>
       </c>
@@ -7265,8 +7430,11 @@
       <c r="AP56">
         <v>1</v>
       </c>
+      <c r="AQ56">
+        <v>3</v>
+      </c>
     </row>
-    <row r="57" spans="1:42">
+    <row r="57" spans="1:43">
       <c r="A57" s="1">
         <v>0.81</v>
       </c>
@@ -7366,8 +7534,11 @@
       <c r="AP57">
         <v>5</v>
       </c>
+      <c r="AQ57">
+        <v>2</v>
+      </c>
     </row>
-    <row r="58" spans="1:42">
+    <row r="58" spans="1:43">
       <c r="A58" s="1">
         <v>0.82</v>
       </c>
@@ -7467,8 +7638,11 @@
       <c r="AP58">
         <v>5</v>
       </c>
+      <c r="AQ58">
+        <v>3</v>
+      </c>
     </row>
-    <row r="59" spans="1:42">
+    <row r="59" spans="1:43">
       <c r="A59" s="1">
         <v>0.22</v>
       </c>
@@ -7568,8 +7742,11 @@
       <c r="AP59">
         <v>5</v>
       </c>
+      <c r="AQ59">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="1:42">
+    <row r="60" spans="1:43">
       <c r="A60" s="1">
         <v>0.12</v>
       </c>
@@ -7669,8 +7846,11 @@
       <c r="AP60">
         <v>5</v>
       </c>
+      <c r="AQ60">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="1:42">
+    <row r="61" spans="1:43">
       <c r="A61" s="1">
         <v>0</v>
       </c>
@@ -7770,8 +7950,11 @@
       <c r="AP61">
         <v>1</v>
       </c>
+      <c r="AQ61">
+        <v>3</v>
+      </c>
     </row>
-    <row r="62" spans="1:42">
+    <row r="62" spans="1:43">
       <c r="A62" s="1">
         <v>0.78</v>
       </c>
@@ -7871,8 +8054,11 @@
       <c r="AP62">
         <v>5</v>
       </c>
+      <c r="AQ62">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="1:42">
+    <row r="63" spans="1:43">
       <c r="A63" s="1">
         <v>0.89</v>
       </c>
@@ -7972,8 +8158,11 @@
       <c r="AP63">
         <v>5</v>
       </c>
+      <c r="AQ63">
+        <v>3</v>
+      </c>
     </row>
-    <row r="64" spans="1:42">
+    <row r="64" spans="1:43">
       <c r="A64" s="1">
         <v>0.04</v>
       </c>
@@ -8073,8 +8262,11 @@
       <c r="AP64">
         <v>5</v>
       </c>
+      <c r="AQ64">
+        <v>3</v>
+      </c>
     </row>
-    <row r="65" spans="1:42">
+    <row r="65" spans="1:43">
       <c r="A65" s="1">
         <v>0.05</v>
       </c>
@@ -8174,8 +8366,11 @@
       <c r="AP65">
         <v>1</v>
       </c>
+      <c r="AQ65">
+        <v>3</v>
+      </c>
     </row>
-    <row r="66" spans="1:42">
+    <row r="66" spans="1:43">
       <c r="A66" s="1">
         <v>0.13</v>
       </c>
@@ -8275,8 +8470,11 @@
       <c r="AP66">
         <v>5</v>
       </c>
+      <c r="AQ66">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="1:42">
+    <row r="67" spans="1:43">
       <c r="A67" s="1">
         <v>0</v>
       </c>
@@ -8385,8 +8583,11 @@
       <c r="AP67">
         <v>2</v>
       </c>
+      <c r="AQ67">
+        <v>1</v>
+      </c>
     </row>
-    <row r="68" spans="1:42">
+    <row r="68" spans="1:43">
       <c r="A68" s="1">
         <v>0.06</v>
       </c>
@@ -8485,6 +8686,9 @@
       </c>
       <c r="AP68">
         <v>5</v>
+      </c>
+      <c r="AQ68">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/price.xlsx
+++ b/price.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="177">
   <si>
     <t>浅海</t>
   </si>
@@ -157,205 +157,921 @@
     <t>南极磷虾</t>
   </si>
   <si>
+    <t>简介</t>
+  </si>
+  <si>
     <t>翻车鱼</t>
   </si>
   <si>
+    <t>经常侧翻漂在海面晒太阳 温顺但巨大无比</t>
+  </si>
+  <si>
     <t>蓝鳍金枪鱼</t>
   </si>
   <si>
+    <t>我真的钓到它了嘛</t>
+  </si>
+  <si>
     <t>大王乌贼</t>
   </si>
   <si>
+    <t>传奇物种</t>
+  </si>
+  <si>
     <t>长尾鲨</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尾鳍非常长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>相当少见</t>
+    </r>
+  </si>
+  <si>
     <t>巨石斑鱼</t>
   </si>
   <si>
+    <t>巨大的底栖鱼 体重能到几百公斤</t>
+  </si>
+  <si>
     <t>魔鬼鱼</t>
   </si>
   <si>
+    <r>
+      <t>与名字不同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>性格温和</t>
+    </r>
+  </si>
+  <si>
     <t>皇带鱼</t>
   </si>
   <si>
+    <t>头顶红色鳍冠 超级长</t>
+  </si>
+  <si>
     <t>鼠鲨</t>
   </si>
   <si>
+    <r>
+      <t>体温比水高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>能在冷水区高速巡猎</t>
+    </r>
+  </si>
+  <si>
     <t>青鲨</t>
   </si>
   <si>
+    <t>细长优雅 背部亮蓝 美丽危险</t>
+  </si>
+  <si>
     <t>旗鱼</t>
   </si>
   <si>
+    <t>传奇般的速度 垂钓者的明珠</t>
+  </si>
+  <si>
     <t>皱筛鲨</t>
   </si>
   <si>
+    <t>深海鲨鱼 嘴长在最前面而非腹下</t>
+  </si>
+  <si>
     <t>刺魟</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>平时埋在沙里只露出眼睛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尾巴上的毒刺是最后手段</t>
+    </r>
+  </si>
+  <si>
     <t>牛港鲹</t>
   </si>
   <si>
+    <r>
+      <t>额头又陡又硬</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>浅水追猎时连低飞的海鸟都能扑下来</t>
+    </r>
+  </si>
+  <si>
     <t>犁头鳐</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头扁得像把铲子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>身子却拖着条鲨鱼尾</t>
+    </r>
+  </si>
+  <si>
     <t>长鳍金枪鱼</t>
   </si>
   <si>
+    <t>胸鳍长得出奇</t>
+  </si>
+  <si>
     <t>月鱼</t>
   </si>
   <si>
+    <t>少有的能自己产热的硬骨鱼</t>
+  </si>
+  <si>
     <t>海湾鲟</t>
   </si>
   <si>
+    <r>
+      <t>没有鳞片</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>沿着身体排了几列骨板</t>
+    </r>
+  </si>
+  <si>
     <t>高体鰤</t>
   </si>
   <si>
+    <t>身板高厚结实 很受欢迎的鱼类</t>
+  </si>
+  <si>
     <t>红尾梭鱼</t>
   </si>
   <si>
+    <t>机动性很好的小型鱼</t>
+  </si>
+  <si>
     <t>真蛸</t>
   </si>
   <si>
+    <t>被逼急了就喷墨跑路</t>
+  </si>
+  <si>
     <t>裸胸鳝</t>
   </si>
   <si>
+    <r>
+      <t>躲在礁缝里只露出脑袋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>嘴一张一合其实只是在呼吸</t>
+    </r>
+  </si>
+  <si>
     <t>海狼鱼</t>
   </si>
   <si>
+    <t>咬合力惊人 成群结队</t>
+  </si>
+  <si>
     <t>海鲇‌</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>背鳍藏着毒刺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>摘钩时千万别大意</t>
+    </r>
+  </si>
+  <si>
     <t>马鲛鱼</t>
   </si>
   <si>
+    <t>高速巡游 咬钩瞬间像挂上了一辆摩托车</t>
+  </si>
+  <si>
     <t>真鲷</t>
   </si>
   <si>
+    <t>美味且常见的鱼类 有很多种吃法</t>
+  </si>
+  <si>
     <t>东星斑</t>
   </si>
   <si>
+    <t>珊瑚礁里最贵的住户</t>
+  </si>
+  <si>
     <t>牙鲆</t>
   </si>
   <si>
+    <t>平趴在海底 两只眼睛长在同一侧</t>
+  </si>
+  <si>
     <t>金眼鲈</t>
   </si>
   <si>
+    <t>以巨大的拉力闻名</t>
+  </si>
+  <si>
     <t>河豚</t>
   </si>
   <si>
+    <r>
+      <t>圆滚滚的小家伙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>生气时会把自己吹成球</t>
+    </r>
+  </si>
+  <si>
     <t>黑鲷</t>
   </si>
   <si>
+    <t>激流中的黑影 警觉且贪嘴</t>
+  </si>
+  <si>
     <t>带鱼</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>像一把银色的剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在深处垂直游动</t>
+    </r>
+  </si>
+  <si>
     <t>鲈鱼</t>
   </si>
   <si>
+    <r>
+      <t>新手的老朋友了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无论何时都愿意咬钩</t>
+    </r>
+  </si>
+  <si>
     <t>椰子海螺</t>
   </si>
   <si>
+    <r>
+      <t>壳大得像颗椰子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>搬起来得用两只手</t>
+    </r>
+  </si>
+  <si>
     <t>金鲳鱼‌</t>
   </si>
   <si>
+    <t>扁扁的菱形身板 相当有力量</t>
+  </si>
+  <si>
     <t>帆蜥</t>
   </si>
   <si>
+    <t>背上竖着一面大帆 深海鱼类 嘴也大得离谱</t>
+  </si>
+  <si>
     <t>灰仙鱼</t>
   </si>
   <si>
+    <t>扁扁的身子贴着珊瑚礁绕来绕去</t>
+  </si>
+  <si>
     <t>鹦鹉螺</t>
   </si>
   <si>
+    <t>几亿年没怎么变过样 通过气室控制浮沉</t>
+  </si>
+  <si>
     <t>鼠尾鳕</t>
   </si>
   <si>
+    <t>大脑袋拖着根越来越细的尾巴 长年待在几百米深的海底</t>
+  </si>
+  <si>
     <t>褐拟鳞鲀</t>
   </si>
   <si>
+    <t>皮厚牙硬 领地意识强 会主动追人</t>
+  </si>
+  <si>
     <t>枪鱿</t>
   </si>
   <si>
+    <t>比章鱼多两条触手 群体行动</t>
+  </si>
+  <si>
     <t>香蕉鱼</t>
   </si>
   <si>
+    <t>小陈的最爱</t>
+  </si>
+  <si>
     <t>鲭‌鱼</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>背上一道道深色波纹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成群结队</t>
+    </r>
+  </si>
+  <si>
     <t>绿毒鲉</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伪装成礁石趴着一动不动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>背鳍藏着剧毒</t>
+    </r>
+  </si>
+  <si>
     <t>鲍</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单片壳紧紧吸在岩壁上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>要费大力气才能撬下来</t>
+    </r>
+  </si>
+  <si>
     <t>刺尻鱼</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>体色鲜艳</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个头不大脾气不小</t>
+    </r>
+  </si>
+  <si>
     <t>竹荚鱼</t>
   </si>
   <si>
+    <t>体侧有一排硬棱鳞 从头排到尾</t>
+  </si>
+  <si>
     <t>棘海星</t>
   </si>
   <si>
+    <t>粗糙的表面 很常见的海星</t>
+  </si>
+  <si>
     <t>马夫鱼</t>
   </si>
   <si>
+    <t>背鳍拖出一根长长的白色飘带</t>
+  </si>
+  <si>
     <t>红海星</t>
   </si>
   <si>
+    <t>小型海星</t>
+  </si>
+  <si>
     <t>黑蝴蝶鱼</t>
   </si>
   <si>
+    <t>比普通的蝴蝶鱼略大一些 颜色较深</t>
+  </si>
+  <si>
     <t>蓝指海星</t>
   </si>
   <si>
+    <t>真是奇怪的颜色</t>
+  </si>
+  <si>
     <t>拟花鮨</t>
   </si>
   <si>
+    <r>
+      <t>成群悬在珊瑚上方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>粉粉紫紫的一片</t>
+    </r>
+  </si>
+  <si>
     <t>蓝圆鲹</t>
   </si>
   <si>
+    <t>小个头 但圆鼓鼓的 肉很多</t>
+  </si>
+  <si>
     <t>扇贝</t>
   </si>
   <si>
+    <t>撬开有惊喜</t>
+  </si>
+  <si>
     <t>蝴蝶鱼</t>
   </si>
   <si>
+    <t>尾巴附近的亮色 让天敌分不清头和尾</t>
+  </si>
+  <si>
     <t>小丑鱼（伯爵）</t>
   </si>
   <si>
+    <t>小丑鱼的特殊个体 花纹更醒目</t>
+  </si>
+  <si>
     <t>紫海胆</t>
   </si>
   <si>
+    <t>一身紫色长刺 底下藏着五颗牙的小嘴</t>
+  </si>
+  <si>
     <t>小丑鱼</t>
   </si>
   <si>
+    <t>住在海葵触手里但并不怕蛰 名气相当大的小鱼</t>
+  </si>
+  <si>
     <t>大鳍弹涂鱼</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>背鳍又高又大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>爬上泥滩后会竖起来炫耀</t>
+    </r>
+  </si>
+  <si>
     <t>秋刀鱼</t>
   </si>
   <si>
+    <t>细长的小鱼 非常美味</t>
+  </si>
+  <si>
     <t>文蛤</t>
   </si>
   <si>
+    <t>比蛤蜊更大 贝壳也更厚重</t>
+  </si>
+  <si>
     <t>蛤蜊</t>
   </si>
   <si>
+    <t>退潮后沙滩上到处是小孔 往下一挖就能翻出来</t>
+  </si>
+  <si>
     <t>‌弹涂鱼</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以用胸鳍跳着走</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>离了水也活得自在</t>
+    </r>
+  </si>
+  <si>
     <t>沙丁鱼</t>
   </si>
   <si>
+    <t>以恐怖的规模群体行动 但也会吸引大猎食者</t>
+  </si>
+  <si>
     <t>贻贝</t>
   </si>
   <si>
+    <t>用丝互相连接 像是钓到了麻袋</t>
+  </si>
+  <si>
     <t>鞭冠鱼</t>
   </si>
   <si>
+    <r>
+      <t>头顶伸出一根长长的钓竿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在漆黑深海里钓比自己小的鱼</t>
+    </r>
+  </si>
+  <si>
     <t>银斧鱼</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>身子薄得像片刀刃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.5"/>
+        <color rgb="FF1F2328"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>肚子上一排发光器</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -369,7 +1085,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +1100,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF1F2328"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -529,8 +1251,14 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.5"/>
+      <color rgb="FF1F2328"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -540,6 +1268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -889,16 +1623,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -907,37 +1638,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
@@ -952,74 +1683,77 @@
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1030,11 +1764,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1346,10 +2089,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AQ68"/>
+  <dimension ref="A1:AR68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="44" max="44" width="47.2833333333333" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43">
+    <row r="1" spans="1:44">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1479,8 +2225,11 @@
       <c r="AQ1" t="s">
         <v>18</v>
       </c>
+      <c r="AR1" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:44">
       <c r="A2" s="1">
         <v>0.03</v>
       </c>
@@ -1541,8 +2290,8 @@
       <c r="T2" s="1">
         <v>6</v>
       </c>
-      <c r="U2" s="4" t="s">
-        <v>42</v>
+      <c r="U2" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="V2" s="1">
         <v>150</v>
@@ -1583,8 +2332,11 @@
       <c r="AQ2">
         <v>2</v>
       </c>
+      <c r="AR2" s="6" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="3" spans="1:43">
+    <row r="3" spans="1:44">
       <c r="A3" s="1">
         <v>0.02</v>
       </c>
@@ -1645,8 +2397,8 @@
       <c r="T3" s="1">
         <v>22</v>
       </c>
-      <c r="U3" s="4" t="s">
-        <v>43</v>
+      <c r="U3" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="V3" s="1">
         <v>30</v>
@@ -1687,8 +2439,11 @@
       <c r="AQ3">
         <v>1</v>
       </c>
+      <c r="AR3" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="4" spans="1:43">
+    <row r="4" spans="1:44">
       <c r="A4" s="1">
         <v>0.09</v>
       </c>
@@ -1749,8 +2504,8 @@
       <c r="T4" s="1">
         <v>17</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>44</v>
+      <c r="U4" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="V4" s="1">
         <v>37.5</v>
@@ -1791,8 +2546,11 @@
       <c r="AQ4">
         <v>1</v>
       </c>
+      <c r="AR4" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="5" spans="1:43">
+    <row r="5" ht="14.25" spans="1:44">
       <c r="A5" s="1">
         <v>0.1</v>
       </c>
@@ -1853,8 +2611,8 @@
       <c r="T5" s="1">
         <v>15</v>
       </c>
-      <c r="U5" s="4" t="s">
-        <v>45</v>
+      <c r="U5" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="V5" s="1">
         <v>6</v>
@@ -1895,8 +2653,11 @@
       <c r="AQ5">
         <v>1</v>
       </c>
+      <c r="AR5" s="6" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="6" spans="1:43">
+    <row r="6" spans="1:44">
       <c r="A6" s="1">
         <v>0.08</v>
       </c>
@@ -1957,8 +2718,8 @@
       <c r="T6" s="1">
         <v>17</v>
       </c>
-      <c r="U6" s="4" t="s">
-        <v>46</v>
+      <c r="U6" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="V6" s="1">
         <v>7.5</v>
@@ -1999,8 +2760,11 @@
       <c r="AQ6">
         <v>1</v>
       </c>
+      <c r="AR6" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="7" spans="1:43">
+    <row r="7" ht="14.25" spans="1:44">
       <c r="A7" s="1">
         <v>0.08</v>
       </c>
@@ -2061,8 +2825,8 @@
       <c r="T7" s="1">
         <v>4</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>47</v>
+      <c r="U7" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="V7" s="1">
         <v>15</v>
@@ -2103,8 +2867,11 @@
       <c r="AQ7">
         <v>2</v>
       </c>
+      <c r="AR7" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="8" spans="1:43">
+    <row r="8" spans="1:44">
       <c r="A8" s="1">
         <v>0.15</v>
       </c>
@@ -2165,8 +2932,8 @@
       <c r="T8" s="1">
         <v>22</v>
       </c>
-      <c r="U8" s="4" t="s">
-        <v>48</v>
+      <c r="U8" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="V8" s="1">
         <v>15</v>
@@ -2207,8 +2974,11 @@
       <c r="AQ8">
         <v>1</v>
       </c>
+      <c r="AR8" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="9" spans="1:43">
+    <row r="9" ht="14.25" spans="1:44">
       <c r="A9" s="1">
         <v>0.03</v>
       </c>
@@ -2269,8 +3039,8 @@
       <c r="T9" s="1">
         <v>7</v>
       </c>
-      <c r="U9" s="4" t="s">
-        <v>49</v>
+      <c r="U9" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="V9" s="1">
         <v>18</v>
@@ -2311,8 +3081,11 @@
       <c r="AQ9">
         <v>2</v>
       </c>
+      <c r="AR9" s="7" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="10" spans="1:43">
+    <row r="10" spans="1:44">
       <c r="A10" s="1">
         <v>0.04</v>
       </c>
@@ -2373,8 +3146,8 @@
       <c r="T10" s="1">
         <v>12</v>
       </c>
-      <c r="U10" s="4" t="s">
-        <v>50</v>
+      <c r="U10" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="V10" s="1">
         <v>12</v>
@@ -2415,8 +3188,11 @@
       <c r="AQ10">
         <v>1</v>
       </c>
+      <c r="AR10" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="11" spans="1:43">
+    <row r="11" spans="1:44">
       <c r="A11" s="1">
         <v>0.68</v>
       </c>
@@ -2453,7 +3229,7 @@
       <c r="L11" s="1">
         <v>0.05</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="8">
         <v>0.2</v>
       </c>
       <c r="N11" s="1">
@@ -2477,8 +3253,8 @@
       <c r="T11" s="1">
         <v>10</v>
       </c>
-      <c r="U11" s="4" t="s">
-        <v>51</v>
+      <c r="U11" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="V11" s="1">
         <v>12</v>
@@ -2519,8 +3295,11 @@
       <c r="AQ11">
         <v>1</v>
       </c>
+      <c r="AR11" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="12" spans="1:43">
+    <row r="12" spans="1:44">
       <c r="A12" s="1">
         <v>0.03</v>
       </c>
@@ -2557,7 +3336,7 @@
       <c r="L12" s="1">
         <v>0.05</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="8">
         <v>0.2</v>
       </c>
       <c r="N12" s="1">
@@ -2581,8 +3360,8 @@
       <c r="T12" s="1">
         <v>17</v>
       </c>
-      <c r="U12" s="4" t="s">
-        <v>52</v>
+      <c r="U12" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="V12" s="1">
         <v>6</v>
@@ -2623,8 +3402,11 @@
       <c r="AQ12">
         <v>1</v>
       </c>
+      <c r="AR12" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="13" spans="1:43">
+    <row r="13" ht="14.25" spans="1:44">
       <c r="A13" s="1">
         <v>0.07</v>
       </c>
@@ -2661,7 +3443,7 @@
       <c r="L13" s="1">
         <v>0.05</v>
       </c>
-      <c r="M13" s="5">
+      <c r="M13" s="8">
         <v>0.2</v>
       </c>
       <c r="N13" s="1">
@@ -2685,8 +3467,8 @@
       <c r="T13" s="1">
         <v>6</v>
       </c>
-      <c r="U13" s="4" t="s">
-        <v>53</v>
+      <c r="U13" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="V13" s="1">
         <v>4.5</v>
@@ -2727,8 +3509,11 @@
       <c r="AQ13">
         <v>3</v>
       </c>
+      <c r="AR13" s="6" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" ht="14.25" spans="1:44">
       <c r="A14" s="1">
         <v>0.1</v>
       </c>
@@ -2789,8 +3574,8 @@
       <c r="T14" s="1">
         <v>4</v>
       </c>
-      <c r="U14" s="6" t="s">
-        <v>54</v>
+      <c r="U14" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="V14" s="1">
         <v>2.25</v>
@@ -2840,8 +3625,11 @@
       <c r="AQ14">
         <v>3</v>
       </c>
+      <c r="AR14" s="7" t="s">
+        <v>68</v>
+      </c>
     </row>
-    <row r="15" spans="1:43">
+    <row r="15" ht="14.25" spans="1:44">
       <c r="A15" s="1">
         <v>0.01</v>
       </c>
@@ -2902,8 +3690,8 @@
       <c r="T15" s="1">
         <v>7</v>
       </c>
-      <c r="U15" s="6" t="s">
-        <v>55</v>
+      <c r="U15" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="V15" s="1">
         <v>3</v>
@@ -2953,8 +3741,11 @@
       <c r="AQ15">
         <v>3</v>
       </c>
+      <c r="AR15" s="7" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="16" spans="1:43">
+    <row r="16" spans="1:44">
       <c r="A16" s="1">
         <v>0.05</v>
       </c>
@@ -3015,8 +3806,8 @@
       <c r="T16" s="1">
         <v>12</v>
       </c>
-      <c r="U16" s="6" t="s">
-        <v>56</v>
+      <c r="U16" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="V16" s="1">
         <v>5.25</v>
@@ -3066,8 +3857,11 @@
       <c r="AQ16">
         <v>2</v>
       </c>
+      <c r="AR16" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="17" spans="1:43">
+    <row r="17" spans="1:44">
       <c r="A17" s="1">
         <v>0.05</v>
       </c>
@@ -3128,8 +3922,8 @@
       <c r="T17" s="1">
         <v>17</v>
       </c>
-      <c r="U17" s="6" t="s">
-        <v>57</v>
+      <c r="U17" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="V17" s="1">
         <v>3</v>
@@ -3179,8 +3973,11 @@
       <c r="AQ17">
         <v>1</v>
       </c>
+      <c r="AR17" s="6" t="s">
+        <v>74</v>
+      </c>
     </row>
-    <row r="18" spans="1:43">
+    <row r="18" ht="14.25" spans="1:44">
       <c r="A18" s="1">
         <v>0.08</v>
       </c>
@@ -3241,8 +4038,8 @@
       <c r="T18" s="1">
         <v>10</v>
       </c>
-      <c r="U18" s="6" t="s">
-        <v>58</v>
+      <c r="U18" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="V18" s="1">
         <v>2.25</v>
@@ -3292,8 +4089,11 @@
       <c r="AQ18">
         <v>2</v>
       </c>
+      <c r="AR18" s="7" t="s">
+        <v>76</v>
+      </c>
     </row>
-    <row r="19" spans="1:43">
+    <row r="19" spans="1:44">
       <c r="A19" s="1">
         <v>0.06</v>
       </c>
@@ -3354,8 +4154,8 @@
       <c r="T19" s="1">
         <v>7</v>
       </c>
-      <c r="U19" s="6" t="s">
-        <v>59</v>
+      <c r="U19" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="V19" s="1">
         <v>1.2</v>
@@ -3405,8 +4205,11 @@
       <c r="AQ19">
         <v>2</v>
       </c>
+      <c r="AR19" s="7" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="20" spans="1:43">
+    <row r="20" spans="1:44">
       <c r="A20" s="1">
         <v>0.13</v>
       </c>
@@ -3437,7 +4240,7 @@
       <c r="J20" s="1">
         <v>0.75</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="8">
         <v>0.2</v>
       </c>
       <c r="L20" s="1">
@@ -3468,7 +4271,7 @@
         <v>10</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="V20" s="1">
         <v>0.09</v>
@@ -3509,8 +4312,11 @@
       <c r="AQ20">
         <v>3</v>
       </c>
+      <c r="AR20" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="21" spans="1:43">
+    <row r="21" spans="1:44">
       <c r="A21" s="1">
         <v>0.17</v>
       </c>
@@ -3541,7 +4347,7 @@
       <c r="J21" s="1">
         <v>0.2</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="8">
         <v>0.6</v>
       </c>
       <c r="L21" s="1">
@@ -3571,8 +4377,8 @@
       <c r="T21" s="1">
         <v>27</v>
       </c>
-      <c r="U21" s="7" t="s">
-        <v>61</v>
+      <c r="U21" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="V21" s="1">
         <v>0.3</v>
@@ -3622,8 +4428,11 @@
       <c r="AQ21">
         <v>2</v>
       </c>
+      <c r="AR21" t="s">
+        <v>82</v>
+      </c>
     </row>
-    <row r="22" spans="1:43">
+    <row r="22" ht="14.25" spans="1:44">
       <c r="A22" s="1">
         <v>0.04</v>
       </c>
@@ -3684,8 +4493,8 @@
       <c r="T22" s="1">
         <v>14</v>
       </c>
-      <c r="U22" s="8" t="s">
-        <v>62</v>
+      <c r="U22" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="V22" s="1">
         <v>0.45</v>
@@ -3735,8 +4544,11 @@
       <c r="AQ22">
         <v>2</v>
       </c>
+      <c r="AR22" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="23" spans="1:43">
+    <row r="23" spans="1:44">
       <c r="A23" s="1">
         <v>0.08</v>
       </c>
@@ -3797,8 +4609,8 @@
       <c r="T23" s="1">
         <v>7</v>
       </c>
-      <c r="U23" s="8" t="s">
-        <v>63</v>
+      <c r="U23" s="11" t="s">
+        <v>85</v>
       </c>
       <c r="V23" s="1">
         <v>0.75</v>
@@ -3848,8 +4660,11 @@
       <c r="AQ23">
         <v>3</v>
       </c>
+      <c r="AR23" s="6" t="s">
+        <v>86</v>
+      </c>
     </row>
-    <row r="24" spans="1:43">
+    <row r="24" ht="14.25" spans="1:44">
       <c r="A24" s="1">
         <v>0.13</v>
       </c>
@@ -3910,8 +4725,8 @@
       <c r="T24" s="1">
         <v>4</v>
       </c>
-      <c r="U24" s="8" t="s">
-        <v>64</v>
+      <c r="U24" s="11" t="s">
+        <v>87</v>
       </c>
       <c r="V24" s="1">
         <v>0.45</v>
@@ -3961,8 +4776,11 @@
       <c r="AQ24">
         <v>3</v>
       </c>
+      <c r="AR24" s="6" t="s">
+        <v>88</v>
+      </c>
     </row>
-    <row r="25" spans="1:43">
+    <row r="25" spans="1:44">
       <c r="A25" s="1">
         <v>0.88</v>
       </c>
@@ -4023,8 +4841,8 @@
       <c r="T25" s="1">
         <v>6</v>
       </c>
-      <c r="U25" s="6" t="s">
-        <v>65</v>
+      <c r="U25" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="V25" s="1">
         <v>1.8</v>
@@ -4074,8 +4892,11 @@
       <c r="AQ25">
         <v>2</v>
       </c>
+      <c r="AR25" s="6" t="s">
+        <v>90</v>
+      </c>
     </row>
-    <row r="26" spans="1:43">
+    <row r="26" spans="1:44">
       <c r="A26" s="1">
         <v>0.07</v>
       </c>
@@ -4106,7 +4927,7 @@
       <c r="J26" s="1">
         <v>0.2</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K26" s="8">
         <v>0.6</v>
       </c>
       <c r="L26" s="1">
@@ -4136,8 +4957,8 @@
       <c r="T26" s="1">
         <v>16</v>
       </c>
-      <c r="U26" s="7" t="s">
-        <v>66</v>
+      <c r="U26" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="V26" s="1">
         <v>0.15</v>
@@ -4187,8 +5008,11 @@
       <c r="AQ26">
         <v>3</v>
       </c>
+      <c r="AR26" s="6" t="s">
+        <v>92</v>
+      </c>
     </row>
-    <row r="27" spans="1:43">
+    <row r="27" spans="1:44">
       <c r="A27" s="1">
         <v>0.1</v>
       </c>
@@ -4249,8 +5073,8 @@
       <c r="T27" s="1">
         <v>47</v>
       </c>
-      <c r="U27" s="8" t="s">
-        <v>67</v>
+      <c r="U27" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="V27" s="1">
         <v>0.375</v>
@@ -4300,8 +5124,11 @@
       <c r="AQ27">
         <v>1</v>
       </c>
+      <c r="AR27" s="6" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="28" spans="1:43">
+    <row r="28" spans="1:44">
       <c r="A28" s="1">
         <v>0</v>
       </c>
@@ -4332,7 +5159,7 @@
       <c r="J28" s="1">
         <v>0.2</v>
       </c>
-      <c r="K28" s="5">
+      <c r="K28" s="8">
         <v>0.6</v>
       </c>
       <c r="L28" s="1">
@@ -4362,8 +5189,8 @@
       <c r="T28" s="1">
         <v>7</v>
       </c>
-      <c r="U28" s="7" t="s">
-        <v>68</v>
+      <c r="U28" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="V28" s="1">
         <v>0.225</v>
@@ -4413,8 +5240,11 @@
       <c r="AQ28">
         <v>2</v>
       </c>
+      <c r="AR28" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
-    <row r="29" spans="1:43">
+    <row r="29" spans="1:44">
       <c r="A29" s="1">
         <v>0.15</v>
       </c>
@@ -4475,8 +5305,8 @@
       <c r="T29" s="1">
         <v>4</v>
       </c>
-      <c r="U29" s="6" t="s">
-        <v>69</v>
+      <c r="U29" s="9" t="s">
+        <v>97</v>
       </c>
       <c r="V29" s="1">
         <v>1.8</v>
@@ -4526,8 +5356,11 @@
       <c r="AQ29">
         <v>2</v>
       </c>
+      <c r="AR29" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="30" spans="1:43">
+    <row r="30" ht="14.25" spans="1:44">
       <c r="A30" s="1">
         <v>0.09</v>
       </c>
@@ -4558,7 +5391,7 @@
       <c r="J30" s="1">
         <v>0.75</v>
       </c>
-      <c r="K30" s="5">
+      <c r="K30" s="8">
         <v>0.2</v>
       </c>
       <c r="L30" s="1">
@@ -4589,7 +5422,7 @@
         <v>1</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="V30" s="1">
         <v>0.15</v>
@@ -4630,8 +5463,11 @@
       <c r="AQ30">
         <v>3</v>
       </c>
+      <c r="AR30" s="7" t="s">
+        <v>100</v>
+      </c>
     </row>
-    <row r="31" spans="1:43">
+    <row r="31" spans="1:44">
       <c r="A31" s="1">
         <v>0.06</v>
       </c>
@@ -4662,7 +5498,7 @@
       <c r="J31" s="1">
         <v>0.2</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31" s="8">
         <v>0.6</v>
       </c>
       <c r="L31" s="1">
@@ -4692,8 +5528,8 @@
       <c r="T31" s="1">
         <v>26</v>
       </c>
-      <c r="U31" s="7" t="s">
-        <v>71</v>
+      <c r="U31" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="V31" s="1">
         <v>0.12</v>
@@ -4743,8 +5579,11 @@
       <c r="AQ31">
         <v>3</v>
       </c>
+      <c r="AR31" s="6" t="s">
+        <v>102</v>
+      </c>
     </row>
-    <row r="32" spans="1:43">
+    <row r="32" ht="14.25" spans="1:44">
       <c r="A32" s="1">
         <v>0.07</v>
       </c>
@@ -4805,8 +5644,8 @@
       <c r="T32" s="1">
         <v>27</v>
       </c>
-      <c r="U32" s="8" t="s">
-        <v>72</v>
+      <c r="U32" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="V32" s="1">
         <v>0.3</v>
@@ -4856,8 +5695,11 @@
       <c r="AQ32">
         <v>2</v>
       </c>
+      <c r="AR32" s="6" t="s">
+        <v>104</v>
+      </c>
     </row>
-    <row r="33" spans="1:43">
+    <row r="33" ht="14.25" spans="1:44">
       <c r="A33" s="1">
         <v>0.77</v>
       </c>
@@ -4888,7 +5730,7 @@
       <c r="J33" s="1">
         <v>0.2</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="8">
         <v>0.6</v>
       </c>
       <c r="L33" s="1">
@@ -4918,8 +5760,8 @@
       <c r="T33" s="1">
         <v>4</v>
       </c>
-      <c r="U33" s="7" t="s">
-        <v>73</v>
+      <c r="U33" s="10" t="s">
+        <v>105</v>
       </c>
       <c r="V33" s="1">
         <v>0.255</v>
@@ -4969,8 +5811,11 @@
       <c r="AQ33">
         <v>3</v>
       </c>
+      <c r="AR33" s="7" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="34" spans="1:43">
+    <row r="34" ht="14.25" spans="1:44">
       <c r="A34" s="1">
         <v>0.03</v>
       </c>
@@ -5001,7 +5846,7 @@
       <c r="J34" s="1">
         <v>0.2</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="8">
         <v>0.6</v>
       </c>
       <c r="L34" s="1">
@@ -5031,8 +5876,8 @@
       <c r="T34" s="1">
         <v>17</v>
       </c>
-      <c r="U34" s="7" t="s">
-        <v>74</v>
+      <c r="U34" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="V34" s="1">
         <v>0.15</v>
@@ -5082,8 +5927,11 @@
       <c r="AQ34">
         <v>3</v>
       </c>
+      <c r="AR34" s="6" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="35" spans="1:43">
+    <row r="35" spans="1:44">
       <c r="A35" s="1">
         <v>0.15</v>
       </c>
@@ -5144,8 +5992,8 @@
       <c r="T35" s="1">
         <v>6</v>
       </c>
-      <c r="U35" s="8" t="s">
-        <v>75</v>
+      <c r="U35" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="V35" s="1">
         <v>0.6</v>
@@ -5195,8 +6043,11 @@
       <c r="AQ35">
         <v>3</v>
       </c>
+      <c r="AR35" s="7" t="s">
+        <v>110</v>
+      </c>
     </row>
-    <row r="36" spans="1:43">
+    <row r="36" spans="1:44">
       <c r="A36" s="1">
         <v>0.07</v>
       </c>
@@ -5257,8 +6108,8 @@
       <c r="T36" s="1">
         <v>77</v>
       </c>
-      <c r="U36" s="8" t="s">
-        <v>76</v>
+      <c r="U36" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="V36" s="1">
         <v>0.6</v>
@@ -5308,8 +6159,11 @@
       <c r="AQ36">
         <v>1</v>
       </c>
+      <c r="AR36" s="6" t="s">
+        <v>112</v>
+      </c>
     </row>
-    <row r="37" spans="1:43">
+    <row r="37" spans="1:44">
       <c r="A37" s="1">
         <v>0.11</v>
       </c>
@@ -5340,7 +6194,7 @@
       <c r="J37" s="1">
         <v>0.2</v>
       </c>
-      <c r="K37" s="5">
+      <c r="K37" s="8">
         <v>0.6</v>
       </c>
       <c r="L37" s="1">
@@ -5370,8 +6224,8 @@
       <c r="T37" s="1">
         <v>17</v>
       </c>
-      <c r="U37" s="7" t="s">
-        <v>77</v>
+      <c r="U37" s="10" t="s">
+        <v>113</v>
       </c>
       <c r="V37" s="1">
         <v>0.12</v>
@@ -5421,8 +6275,11 @@
       <c r="AQ37">
         <v>3</v>
       </c>
+      <c r="AR37" s="6" t="s">
+        <v>114</v>
+      </c>
     </row>
-    <row r="38" spans="1:43">
+    <row r="38" spans="1:44">
       <c r="A38" s="1">
         <v>0.07</v>
       </c>
@@ -5453,7 +6310,7 @@
       <c r="J38" s="1">
         <v>0.75</v>
       </c>
-      <c r="K38" s="5">
+      <c r="K38" s="8">
         <v>0.2</v>
       </c>
       <c r="L38" s="1">
@@ -5484,7 +6341,7 @@
         <v>20</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="V38" s="1">
         <v>0.12</v>
@@ -5525,8 +6382,11 @@
       <c r="AQ38">
         <v>3</v>
       </c>
+      <c r="AR38" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
-    <row r="39" spans="1:43">
+    <row r="39" spans="1:44">
       <c r="A39" s="1">
         <v>0.05</v>
       </c>
@@ -5557,7 +6417,7 @@
       <c r="J39" s="1">
         <v>0.2</v>
       </c>
-      <c r="K39" s="5">
+      <c r="K39" s="8">
         <v>0.6</v>
       </c>
       <c r="L39" s="1">
@@ -5587,8 +6447,8 @@
       <c r="T39" s="1">
         <v>140</v>
       </c>
-      <c r="U39" s="7" t="s">
-        <v>79</v>
+      <c r="U39" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="V39" s="1">
         <v>0.15</v>
@@ -5638,8 +6498,11 @@
       <c r="AQ39">
         <v>1</v>
       </c>
+      <c r="AR39" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
-    <row r="40" spans="1:43">
+    <row r="40" spans="1:44">
       <c r="A40" s="1">
         <v>0.18</v>
       </c>
@@ -5700,8 +6563,8 @@
       <c r="T40" s="1">
         <v>10</v>
       </c>
-      <c r="U40" s="8" t="s">
-        <v>80</v>
+      <c r="U40" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="V40" s="1">
         <v>0.9</v>
@@ -5751,8 +6614,11 @@
       <c r="AQ40">
         <v>3</v>
       </c>
+      <c r="AR40" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
-    <row r="41" spans="1:43">
+    <row r="41" spans="1:44">
       <c r="A41" s="1">
         <v>0.03</v>
       </c>
@@ -5783,7 +6649,7 @@
       <c r="J41" s="1">
         <v>0.2</v>
       </c>
-      <c r="K41" s="5">
+      <c r="K41" s="8">
         <v>0.6</v>
       </c>
       <c r="L41" s="1">
@@ -5813,8 +6679,8 @@
       <c r="T41" s="1">
         <v>47</v>
       </c>
-      <c r="U41" s="7" t="s">
-        <v>81</v>
+      <c r="U41" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="V41" s="1">
         <v>0.09</v>
@@ -5864,8 +6730,11 @@
       <c r="AQ41">
         <v>3</v>
       </c>
+      <c r="AR41" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="42" spans="1:43">
+    <row r="42" spans="1:44">
       <c r="A42" s="1">
         <v>0.05</v>
       </c>
@@ -5896,7 +6765,7 @@
       <c r="J42" s="1">
         <v>0.75</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="8">
         <v>0.2</v>
       </c>
       <c r="L42" s="1">
@@ -5927,7 +6796,7 @@
         <v>4</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="V42" s="1">
         <v>0.045</v>
@@ -5968,8 +6837,11 @@
       <c r="AQ42">
         <v>3</v>
       </c>
+      <c r="AR42" t="s">
+        <v>124</v>
+      </c>
     </row>
-    <row r="43" spans="1:43">
+    <row r="43" ht="14.25" spans="1:44">
       <c r="A43" s="1">
         <v>0.14</v>
       </c>
@@ -6000,7 +6872,7 @@
       <c r="J43" s="1">
         <v>0.75</v>
       </c>
-      <c r="K43" s="5">
+      <c r="K43" s="8">
         <v>0.2</v>
       </c>
       <c r="L43" s="1">
@@ -6031,7 +6903,7 @@
         <v>6</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>83</v>
+        <v>125</v>
       </c>
       <c r="V43" s="1">
         <v>0.09</v>
@@ -6072,8 +6944,11 @@
       <c r="AQ43">
         <v>3</v>
       </c>
+      <c r="AR43" s="6" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="44" spans="1:43">
+    <row r="44" ht="14.25" spans="1:44">
       <c r="A44" s="1">
         <v>0.13</v>
       </c>
@@ -6104,7 +6979,7 @@
       <c r="J44" s="1">
         <v>0.75</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K44" s="8">
         <v>0.2</v>
       </c>
       <c r="L44" s="1">
@@ -6135,7 +7010,7 @@
         <v>6</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="V44" s="1">
         <v>0.045</v>
@@ -6176,8 +7051,11 @@
       <c r="AQ44">
         <v>3</v>
       </c>
+      <c r="AR44" s="6" t="s">
+        <v>128</v>
+      </c>
     </row>
-    <row r="45" spans="1:43">
+    <row r="45" ht="14.25" spans="1:44">
       <c r="A45" s="1">
         <v>0.1</v>
       </c>
@@ -6208,7 +7086,7 @@
       <c r="J45" s="1">
         <v>0.75</v>
       </c>
-      <c r="K45" s="5">
+      <c r="K45" s="8">
         <v>0.2</v>
       </c>
       <c r="L45" s="1">
@@ -6239,7 +7117,7 @@
         <v>60</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="V45" s="1">
         <v>0.022</v>
@@ -6280,8 +7158,11 @@
       <c r="AQ45">
         <v>2</v>
       </c>
+      <c r="AR45" s="6" t="s">
+        <v>130</v>
+      </c>
     </row>
-    <row r="46" spans="1:43">
+    <row r="46" ht="14.25" spans="1:44">
       <c r="A46" s="1">
         <v>0.18</v>
       </c>
@@ -6312,7 +7193,7 @@
       <c r="J46" s="1">
         <v>0.75</v>
       </c>
-      <c r="K46" s="5">
+      <c r="K46" s="8">
         <v>0.2</v>
       </c>
       <c r="L46" s="1">
@@ -6343,7 +7224,7 @@
         <v>27</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>86</v>
+        <v>131</v>
       </c>
       <c r="V46" s="1">
         <v>0.03</v>
@@ -6384,8 +7265,11 @@
       <c r="AQ46">
         <v>3</v>
       </c>
+      <c r="AR46" s="6" t="s">
+        <v>132</v>
+      </c>
     </row>
-    <row r="47" spans="1:43">
+    <row r="47" spans="1:44">
       <c r="A47" s="1">
         <v>0.54</v>
       </c>
@@ -6416,7 +7300,7 @@
       <c r="J47" s="1">
         <v>0.75</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K47" s="8">
         <v>0.2</v>
       </c>
       <c r="L47" s="1">
@@ -6447,7 +7331,7 @@
         <v>6</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>87</v>
+        <v>133</v>
       </c>
       <c r="V47" s="1">
         <v>0.09</v>
@@ -6488,8 +7372,11 @@
       <c r="AQ47">
         <v>3</v>
       </c>
+      <c r="AR47" s="6" t="s">
+        <v>134</v>
+      </c>
     </row>
-    <row r="48" spans="1:43">
+    <row r="48" spans="1:44">
       <c r="A48" s="1">
         <v>0.74</v>
       </c>
@@ -6520,7 +7407,7 @@
       <c r="J48" s="1">
         <v>0.75</v>
       </c>
-      <c r="K48" s="5">
+      <c r="K48" s="8">
         <v>0.2</v>
       </c>
       <c r="L48" s="1">
@@ -6551,7 +7438,7 @@
         <v>7</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="V48" s="1">
         <v>0.03</v>
@@ -6592,8 +7479,11 @@
       <c r="AQ48">
         <v>3</v>
       </c>
+      <c r="AR48" t="s">
+        <v>136</v>
+      </c>
     </row>
-    <row r="49" spans="1:43">
+    <row r="49" spans="1:44">
       <c r="A49" s="1">
         <v>0.09</v>
       </c>
@@ -6624,7 +7514,7 @@
       <c r="J49" s="1">
         <v>0.75</v>
       </c>
-      <c r="K49" s="5">
+      <c r="K49" s="8">
         <v>0.2</v>
       </c>
       <c r="L49" s="1">
@@ -6655,7 +7545,7 @@
         <v>17</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="V49" s="1">
         <v>0.022</v>
@@ -6696,8 +7586,11 @@
       <c r="AQ49">
         <v>2</v>
       </c>
+      <c r="AR49" s="6" t="s">
+        <v>138</v>
+      </c>
     </row>
-    <row r="50" spans="1:43">
+    <row r="50" spans="1:44">
       <c r="A50" s="1">
         <v>0.15</v>
       </c>
@@ -6728,7 +7621,7 @@
       <c r="J50" s="1">
         <v>0.75</v>
       </c>
-      <c r="K50" s="5">
+      <c r="K50" s="8">
         <v>0.2</v>
       </c>
       <c r="L50" s="1">
@@ -6759,7 +7652,7 @@
         <v>7</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="V50" s="1">
         <v>0.022</v>
@@ -6800,8 +7693,11 @@
       <c r="AQ50">
         <v>3</v>
       </c>
+      <c r="AR50" t="s">
+        <v>140</v>
+      </c>
     </row>
-    <row r="51" spans="1:43">
+    <row r="51" spans="1:44">
       <c r="A51" s="1">
         <v>0.87</v>
       </c>
@@ -6832,7 +7728,7 @@
       <c r="J51" s="1">
         <v>0.75</v>
       </c>
-      <c r="K51" s="5">
+      <c r="K51" s="8">
         <v>0.2</v>
       </c>
       <c r="L51" s="1">
@@ -6863,7 +7759,7 @@
         <v>17</v>
       </c>
       <c r="U51" s="1" t="s">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="V51" s="1">
         <v>0.018</v>
@@ -6904,8 +7800,11 @@
       <c r="AQ51">
         <v>3</v>
       </c>
+      <c r="AR51" t="s">
+        <v>142</v>
+      </c>
     </row>
-    <row r="52" spans="1:43">
+    <row r="52" spans="1:44">
       <c r="A52" s="1">
         <v>0.04</v>
       </c>
@@ -6936,7 +7835,7 @@
       <c r="J52" s="1">
         <v>0.75</v>
       </c>
-      <c r="K52" s="5">
+      <c r="K52" s="8">
         <v>0.2</v>
       </c>
       <c r="L52" s="1">
@@ -6967,7 +7866,7 @@
         <v>26</v>
       </c>
       <c r="U52" s="1" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="V52" s="1">
         <v>0.015</v>
@@ -7008,8 +7907,11 @@
       <c r="AQ52">
         <v>2</v>
       </c>
+      <c r="AR52" t="s">
+        <v>144</v>
+      </c>
     </row>
-    <row r="53" spans="1:43">
+    <row r="53" ht="14.25" spans="1:44">
       <c r="A53" s="1">
         <v>0.76</v>
       </c>
@@ -7040,7 +7942,7 @@
       <c r="J53" s="1">
         <v>0.75</v>
       </c>
-      <c r="K53" s="5">
+      <c r="K53" s="8">
         <v>0.2</v>
       </c>
       <c r="L53" s="1">
@@ -7071,7 +7973,7 @@
         <v>47</v>
       </c>
       <c r="U53" s="1" t="s">
-        <v>93</v>
+        <v>145</v>
       </c>
       <c r="V53" s="1">
         <v>0.022</v>
@@ -7112,8 +8014,11 @@
       <c r="AQ53">
         <v>2</v>
       </c>
+      <c r="AR53" s="7" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="54" spans="1:43">
+    <row r="54" spans="1:44">
       <c r="A54" s="1">
         <v>0.83</v>
       </c>
@@ -7144,7 +8049,7 @@
       <c r="J54" s="1">
         <v>0.2</v>
       </c>
-      <c r="K54" s="5">
+      <c r="K54" s="8">
         <v>0.6</v>
       </c>
       <c r="L54" s="1">
@@ -7174,8 +8079,8 @@
       <c r="T54" s="1">
         <v>10</v>
       </c>
-      <c r="U54" s="7" t="s">
-        <v>94</v>
+      <c r="U54" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="V54" s="1">
         <v>0.3</v>
@@ -7225,8 +8130,11 @@
       <c r="AQ54">
         <v>3</v>
       </c>
+      <c r="AR54" s="6" t="s">
+        <v>148</v>
+      </c>
     </row>
-    <row r="55" spans="1:43">
+    <row r="55" spans="1:44">
       <c r="A55" s="1">
         <v>0.15</v>
       </c>
@@ -7257,7 +8165,7 @@
       <c r="J55" s="1">
         <v>0.75</v>
       </c>
-      <c r="K55" s="5">
+      <c r="K55" s="8">
         <v>0.2</v>
       </c>
       <c r="L55" s="1">
@@ -7288,7 +8196,7 @@
         <v>70</v>
       </c>
       <c r="U55" s="1" t="s">
-        <v>95</v>
+        <v>149</v>
       </c>
       <c r="V55" s="1">
         <v>0.015</v>
@@ -7329,8 +8237,11 @@
       <c r="AQ55">
         <v>1</v>
       </c>
+      <c r="AR55" s="6" t="s">
+        <v>150</v>
+      </c>
     </row>
-    <row r="56" spans="1:43">
+    <row r="56" spans="1:44">
       <c r="A56" s="1">
         <v>0.13</v>
       </c>
@@ -7361,7 +8272,7 @@
       <c r="J56" s="1">
         <v>0.75</v>
       </c>
-      <c r="K56" s="5">
+      <c r="K56" s="8">
         <v>0.2</v>
       </c>
       <c r="L56" s="1">
@@ -7392,7 +8303,7 @@
         <v>7</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="V56" s="1">
         <v>0.015</v>
@@ -7433,8 +8344,11 @@
       <c r="AQ56">
         <v>3</v>
       </c>
+      <c r="AR56" s="7" t="s">
+        <v>152</v>
+      </c>
     </row>
-    <row r="57" spans="1:43">
+    <row r="57" spans="1:44">
       <c r="A57" s="1">
         <v>0.81</v>
       </c>
@@ -7465,7 +8379,7 @@
       <c r="J57" s="1">
         <v>0.75</v>
       </c>
-      <c r="K57" s="5">
+      <c r="K57" s="8">
         <v>0.2</v>
       </c>
       <c r="L57" s="1">
@@ -7496,7 +8410,7 @@
         <v>60</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="V57" s="1">
         <v>0.003</v>
@@ -7537,8 +8451,11 @@
       <c r="AQ57">
         <v>2</v>
       </c>
+      <c r="AR57" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="58" spans="1:43">
+    <row r="58" spans="1:44">
       <c r="A58" s="1">
         <v>0.82</v>
       </c>
@@ -7569,7 +8486,7 @@
       <c r="J58" s="1">
         <v>0.75</v>
       </c>
-      <c r="K58" s="5">
+      <c r="K58" s="8">
         <v>0.2</v>
       </c>
       <c r="L58" s="1">
@@ -7600,7 +8517,7 @@
         <v>14</v>
       </c>
       <c r="U58" s="1" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="V58" s="1">
         <v>0.003</v>
@@ -7641,8 +8558,11 @@
       <c r="AQ58">
         <v>3</v>
       </c>
+      <c r="AR58" s="6" t="s">
+        <v>156</v>
+      </c>
     </row>
-    <row r="59" spans="1:43">
+    <row r="59" spans="1:44">
       <c r="A59" s="1">
         <v>0.22</v>
       </c>
@@ -7673,7 +8593,7 @@
       <c r="J59" s="1">
         <v>0.75</v>
       </c>
-      <c r="K59" s="5">
+      <c r="K59" s="8">
         <v>0.2</v>
       </c>
       <c r="L59" s="1">
@@ -7704,7 +8624,7 @@
         <v>20</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="V59" s="1">
         <v>0.003</v>
@@ -7745,8 +8665,11 @@
       <c r="AQ59">
         <v>3</v>
       </c>
+      <c r="AR59" s="6" t="s">
+        <v>158</v>
+      </c>
     </row>
-    <row r="60" spans="1:43">
+    <row r="60" ht="14.25" spans="1:44">
       <c r="A60" s="1">
         <v>0.12</v>
       </c>
@@ -7777,7 +8700,7 @@
       <c r="J60" s="1">
         <v>0.75</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K60" s="8">
         <v>0.2</v>
       </c>
       <c r="L60" s="1">
@@ -7808,7 +8731,7 @@
         <v>6</v>
       </c>
       <c r="U60" s="1" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="V60" s="1">
         <v>0.012</v>
@@ -7849,8 +8772,11 @@
       <c r="AQ60">
         <v>3</v>
       </c>
+      <c r="AR60" s="6" t="s">
+        <v>160</v>
+      </c>
     </row>
-    <row r="61" spans="1:43">
+    <row r="61" spans="1:44">
       <c r="A61" s="1">
         <v>0</v>
       </c>
@@ -7881,7 +8807,7 @@
       <c r="J61" s="1">
         <v>0.75</v>
       </c>
-      <c r="K61" s="5">
+      <c r="K61" s="8">
         <v>0.2</v>
       </c>
       <c r="L61" s="1">
@@ -7912,7 +8838,7 @@
         <v>6</v>
       </c>
       <c r="U61" s="1" t="s">
-        <v>101</v>
+        <v>161</v>
       </c>
       <c r="V61" s="1">
         <v>0.012</v>
@@ -7953,8 +8879,11 @@
       <c r="AQ61">
         <v>3</v>
       </c>
+      <c r="AR61" t="s">
+        <v>162</v>
+      </c>
     </row>
-    <row r="62" spans="1:43">
+    <row r="62" spans="1:44">
       <c r="A62" s="1">
         <v>0.78</v>
       </c>
@@ -7985,7 +8914,7 @@
       <c r="J62" s="1">
         <v>0.75</v>
       </c>
-      <c r="K62" s="5">
+      <c r="K62" s="8">
         <v>0.2</v>
       </c>
       <c r="L62" s="1">
@@ -8016,7 +8945,7 @@
         <v>26</v>
       </c>
       <c r="U62" s="1" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="V62" s="1">
         <v>0.007</v>
@@ -8057,8 +8986,11 @@
       <c r="AQ62">
         <v>3</v>
       </c>
+      <c r="AR62" s="6" t="s">
+        <v>164</v>
+      </c>
     </row>
-    <row r="63" spans="1:43">
+    <row r="63" spans="1:44">
       <c r="A63" s="1">
         <v>0.89</v>
       </c>
@@ -8089,7 +9021,7 @@
       <c r="J63" s="1">
         <v>0.75</v>
       </c>
-      <c r="K63" s="5">
+      <c r="K63" s="8">
         <v>0.2</v>
       </c>
       <c r="L63" s="1">
@@ -8120,7 +9052,7 @@
         <v>12</v>
       </c>
       <c r="U63" s="1" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
       <c r="V63" s="1">
         <v>0.004</v>
@@ -8161,8 +9093,11 @@
       <c r="AQ63">
         <v>3</v>
       </c>
+      <c r="AR63" t="s">
+        <v>166</v>
+      </c>
     </row>
-    <row r="64" spans="1:43">
+    <row r="64" ht="14.25" spans="1:44">
       <c r="A64" s="1">
         <v>0.04</v>
       </c>
@@ -8193,7 +9128,7 @@
       <c r="J64" s="1">
         <v>0.75</v>
       </c>
-      <c r="K64" s="5">
+      <c r="K64" s="8">
         <v>0.2</v>
       </c>
       <c r="L64" s="1">
@@ -8224,7 +9159,7 @@
         <v>6</v>
       </c>
       <c r="U64" s="1" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="V64" s="1">
         <v>0.007</v>
@@ -8265,8 +9200,11 @@
       <c r="AQ64">
         <v>3</v>
       </c>
+      <c r="AR64" s="6" t="s">
+        <v>168</v>
+      </c>
     </row>
-    <row r="65" spans="1:43">
+    <row r="65" spans="1:44">
       <c r="A65" s="1">
         <v>0.05</v>
       </c>
@@ -8297,7 +9235,7 @@
       <c r="J65" s="1">
         <v>0.75</v>
       </c>
-      <c r="K65" s="5">
+      <c r="K65" s="8">
         <v>0.2</v>
       </c>
       <c r="L65" s="1">
@@ -8328,7 +9266,7 @@
         <v>16</v>
       </c>
       <c r="U65" s="1" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="V65" s="1">
         <v>0.006</v>
@@ -8369,8 +9307,11 @@
       <c r="AQ65">
         <v>3</v>
       </c>
+      <c r="AR65" t="s">
+        <v>170</v>
+      </c>
     </row>
-    <row r="66" spans="1:43">
+    <row r="66" spans="1:44">
       <c r="A66" s="1">
         <v>0.13</v>
       </c>
@@ -8401,7 +9342,7 @@
       <c r="J66" s="1">
         <v>0.75</v>
       </c>
-      <c r="K66" s="5">
+      <c r="K66" s="8">
         <v>0.2</v>
       </c>
       <c r="L66" s="1">
@@ -8432,7 +9373,7 @@
         <v>6</v>
       </c>
       <c r="U66" s="1" t="s">
-        <v>106</v>
+        <v>171</v>
       </c>
       <c r="V66" s="1">
         <v>0.003</v>
@@ -8473,8 +9414,11 @@
       <c r="AQ66">
         <v>3</v>
       </c>
+      <c r="AR66" t="s">
+        <v>172</v>
+      </c>
     </row>
-    <row r="67" spans="1:43">
+    <row r="67" ht="14.25" spans="1:44">
       <c r="A67" s="1">
         <v>0</v>
       </c>
@@ -8490,7 +9434,7 @@
       <c r="E67" s="1">
         <v>0.72</v>
       </c>
-      <c r="F67" s="5">
+      <c r="F67" s="8">
         <v>0</v>
       </c>
       <c r="G67" s="1">
@@ -8505,7 +9449,7 @@
       <c r="J67" s="1">
         <v>0.2</v>
       </c>
-      <c r="K67" s="5">
+      <c r="K67" s="8">
         <v>0.6</v>
       </c>
       <c r="L67" s="1">
@@ -8535,8 +9479,8 @@
       <c r="T67" s="1">
         <v>270</v>
       </c>
-      <c r="U67" s="7" t="s">
-        <v>107</v>
+      <c r="U67" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="V67" s="1">
         <v>0.3</v>
@@ -8586,8 +9530,11 @@
       <c r="AQ67">
         <v>1</v>
       </c>
+      <c r="AR67" s="7" t="s">
+        <v>174</v>
+      </c>
     </row>
-    <row r="68" spans="1:43">
+    <row r="68" ht="14.25" spans="1:44">
       <c r="A68" s="1">
         <v>0.06</v>
       </c>
@@ -8618,7 +9565,7 @@
       <c r="J68" s="1">
         <v>0.75</v>
       </c>
-      <c r="K68" s="5">
+      <c r="K68" s="8">
         <v>0.2</v>
       </c>
       <c r="L68" s="1">
@@ -8649,7 +9596,7 @@
         <v>270</v>
       </c>
       <c r="U68" s="1" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="V68" s="1">
         <v>0.003</v>
@@ -8689,6 +9636,9 @@
       </c>
       <c r="AQ68">
         <v>1</v>
+      </c>
+      <c r="AR68" s="7" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
